--- a/backend/screener_test_export.xlsx
+++ b/backend/screener_test_export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27521"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pratyush/Websites/screener/company/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FixAdmin\Downloads\fo-sniper-fullstack\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AC4F62-F3F6-2E4B-8F69-3E72AC5D7A2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE8C392-4E46-4FA0-900C-201156C2A97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profit &amp; Loss" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -342,8 +346,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
@@ -464,7 +468,7 @@
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -476,19 +480,19 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="3" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -498,13 +502,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -518,11 +522,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -533,7 +537,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="6" builtinId="5"/>
+    <cellStyle name="Percent" xfId="6" builtinId="5"/>
   </cellStyles>
   <dxfs count="31">
     <dxf>
@@ -1718,23 +1722,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="6" customWidth="1"/>
-    <col min="2" max="6" width="13.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="13.5" style="6" customWidth="1"/>
+    <col min="2" max="6" width="13.44140625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="13.44140625" style="6" customWidth="1"/>
     <col min="12" max="12" width="13.33203125" style="6" customWidth="1"/>
-    <col min="13" max="14" width="12.1640625" style="6" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="6"/>
+    <col min="13" max="13" width="18.109375" style="6" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" style="6" customWidth="1"/>
+    <col min="15" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="str">
         <f>'Data Sheet'!B1</f>
+        <v>RELIANCE INDUSTRIES LTD</v>
       </c>
       <c r="H1" t="str">
         <f>UPDATE</f>
+        <v/>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -1742,39 +1749,49 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16">
         <f>'Data Sheet'!B16</f>
+        <v>42825</v>
       </c>
       <c r="C3" s="16">
         <f>'Data Sheet'!C16</f>
+        <v>43190</v>
       </c>
       <c r="D3" s="16">
         <f>'Data Sheet'!D16</f>
+        <v>43555</v>
       </c>
       <c r="E3" s="16">
         <f>'Data Sheet'!E16</f>
+        <v>43921</v>
       </c>
       <c r="F3" s="16">
         <f>'Data Sheet'!F16</f>
+        <v>44286</v>
       </c>
       <c r="G3" s="16">
         <f>'Data Sheet'!G16</f>
+        <v>44651</v>
       </c>
       <c r="H3" s="16">
         <f>'Data Sheet'!H16</f>
+        <v>45016</v>
       </c>
       <c r="I3" s="16">
         <f>'Data Sheet'!I16</f>
+        <v>45382</v>
       </c>
       <c r="J3" s="16">
         <f>'Data Sheet'!J16</f>
+        <v>45747</v>
       </c>
       <c r="K3" s="16">
         <f>'Data Sheet'!K16</f>
+        <v>46112</v>
       </c>
       <c r="L3" s="17" t="s">
         <v>3</v>
@@ -1786,174 +1803,224 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1">
         <f>'Data Sheet'!B17</f>
+        <v>303954</v>
       </c>
       <c r="C4" s="1">
         <f>'Data Sheet'!C17</f>
+        <v>390823</v>
       </c>
       <c r="D4" s="1">
         <f>'Data Sheet'!D17</f>
+        <v>568337</v>
       </c>
       <c r="E4" s="1">
         <f>'Data Sheet'!E17</f>
+        <v>596679</v>
       </c>
       <c r="F4" s="1">
         <f>'Data Sheet'!F17</f>
+        <v>466307</v>
       </c>
       <c r="G4" s="1">
         <f>'Data Sheet'!G17</f>
+        <v>694673</v>
       </c>
       <c r="H4" s="1">
         <f>'Data Sheet'!H17</f>
+        <v>876396</v>
       </c>
       <c r="I4" s="1">
         <f>'Data Sheet'!I17</f>
+        <v>899041</v>
       </c>
       <c r="J4" s="1">
         <f>'Data Sheet'!J17</f>
+        <v>962820</v>
       </c>
       <c r="K4" s="1">
         <f>'Data Sheet'!K17</f>
+        <v>1055780</v>
       </c>
       <c r="L4" s="1">
         <f>SUM(Quarters!H4:K4)</f>
+        <v>1123055</v>
       </c>
       <c r="M4" s="1">
         <f>$K4+M23*K4</f>
+        <v>1157715.2618350263</v>
       </c>
       <c r="N4" s="1">
         <f>$K4+N23*L4</f>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>1127699.6905806821</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="9">
         <f>SUM('Data Sheet'!B18,'Data Sheet'!B20:B24, -1*'Data Sheet'!B19)</f>
+        <v>257647</v>
       </c>
       <c r="C5" s="9">
         <f>SUM('Data Sheet'!C18,'Data Sheet'!C20:C24, -1*'Data Sheet'!C19)</f>
+        <v>326508</v>
       </c>
       <c r="D5" s="9">
         <f>SUM('Data Sheet'!D18,'Data Sheet'!D20:D24, -1*'Data Sheet'!D19)</f>
+        <v>484087</v>
       </c>
       <c r="E5" s="9">
         <f>SUM('Data Sheet'!E18,'Data Sheet'!E20:E24, -1*'Data Sheet'!E19)</f>
+        <v>507413</v>
       </c>
       <c r="F5" s="9">
         <f>SUM('Data Sheet'!F18,'Data Sheet'!F20:F24, -1*'Data Sheet'!F19)</f>
+        <v>385517</v>
       </c>
       <c r="G5" s="9">
         <f>SUM('Data Sheet'!G18,'Data Sheet'!G20:G24, -1*'Data Sheet'!G19)</f>
+        <v>586092</v>
       </c>
       <c r="H5" s="9">
         <f>SUM('Data Sheet'!H18,'Data Sheet'!H20:H24, -1*'Data Sheet'!H19)</f>
+        <v>734078</v>
       </c>
       <c r="I5" s="9">
         <f>SUM('Data Sheet'!I18,'Data Sheet'!I20:I24, -1*'Data Sheet'!I19)</f>
+        <v>736543</v>
       </c>
       <c r="J5" s="9">
         <f>SUM('Data Sheet'!J18,'Data Sheet'!J20:J24, -1*'Data Sheet'!J19)</f>
+        <v>797222</v>
       </c>
       <c r="K5" s="9">
         <f>SUM('Data Sheet'!K18,'Data Sheet'!K20:K24, -1*'Data Sheet'!K19)</f>
+        <v>876715</v>
       </c>
       <c r="L5" s="9">
         <f>SUM(Quarters!H5:K5)</f>
+        <v>939494</v>
       </c>
       <c r="M5" s="9">
         <f t="shared" ref="M5:N5" si="0">M4-M6</f>
+        <v>956474.59175001108</v>
       </c>
       <c r="N5" s="9">
         <f t="shared" si="0"/>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>943379.52558192378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1">
         <f>B4-B5</f>
+        <v>46307</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" ref="C6:K6" si="1">C4-C5</f>
+        <v>64315</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="1"/>
+        <v>84250</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
+        <v>89266</v>
       </c>
       <c r="F6" s="1">
         <f t="shared" si="1"/>
+        <v>80790</v>
       </c>
       <c r="G6" s="1">
         <f t="shared" si="1"/>
+        <v>108581</v>
       </c>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
+        <v>142318</v>
       </c>
       <c r="I6" s="1">
         <f t="shared" si="1"/>
+        <v>162498</v>
       </c>
       <c r="J6" s="1">
         <f t="shared" si="1"/>
+        <v>165598</v>
       </c>
       <c r="K6" s="1">
         <f t="shared" si="1"/>
+        <v>179065</v>
       </c>
       <c r="L6" s="1">
         <f>SUM(Quarters!H6:K6)</f>
+        <v>183561</v>
       </c>
       <c r="M6" s="1">
         <f>M4*M24</f>
+        <v>201240.67008501518</v>
       </c>
       <c r="N6" s="1">
         <f>N4*N24</f>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+        <v>184320.16499875838</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="9">
         <f>'Data Sheet'!B25</f>
+        <v>9222</v>
       </c>
       <c r="C7" s="9">
         <f>'Data Sheet'!C25</f>
+        <v>9869</v>
       </c>
       <c r="D7" s="9">
         <f>'Data Sheet'!D25</f>
+        <v>8406</v>
       </c>
       <c r="E7" s="9">
         <f>'Data Sheet'!E25</f>
+        <v>8570</v>
       </c>
       <c r="F7" s="9">
         <f>'Data Sheet'!F25</f>
+        <v>22432</v>
       </c>
       <c r="G7" s="9">
         <f>'Data Sheet'!G25</f>
+        <v>19600</v>
       </c>
       <c r="H7" s="9">
         <f>'Data Sheet'!H25</f>
+        <v>12020</v>
       </c>
       <c r="I7" s="9">
         <f>'Data Sheet'!I25</f>
+        <v>15792</v>
       </c>
       <c r="J7" s="9">
         <f>'Data Sheet'!J25</f>
+        <v>17824</v>
       </c>
       <c r="K7" s="9">
         <f>'Data Sheet'!K25</f>
+        <v>28846</v>
       </c>
       <c r="L7" s="9">
         <f>SUM(Quarters!H7:K7)</f>
+        <v>20393</v>
       </c>
       <c r="M7" s="9">
         <v>0</v>
@@ -1962,437 +2029,562 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="9">
         <f>'Data Sheet'!B26</f>
+        <v>11646</v>
       </c>
       <c r="C8" s="9">
         <f>'Data Sheet'!C26</f>
+        <v>16706</v>
       </c>
       <c r="D8" s="9">
         <f>'Data Sheet'!D26</f>
+        <v>20934</v>
       </c>
       <c r="E8" s="9">
         <f>'Data Sheet'!E26</f>
+        <v>22203</v>
       </c>
       <c r="F8" s="9">
         <f>'Data Sheet'!F26</f>
+        <v>26572</v>
       </c>
       <c r="G8" s="9">
         <f>'Data Sheet'!G26</f>
+        <v>29782</v>
       </c>
       <c r="H8" s="9">
         <f>'Data Sheet'!H26</f>
+        <v>40303</v>
       </c>
       <c r="I8" s="9">
         <f>'Data Sheet'!I26</f>
+        <v>50832</v>
       </c>
       <c r="J8" s="9">
         <f>'Data Sheet'!J26</f>
+        <v>53136</v>
       </c>
       <c r="K8" s="9">
         <f>'Data Sheet'!K26</f>
+        <v>57688</v>
       </c>
       <c r="L8" s="9">
         <f>SUM(Quarters!H8:K8)</f>
+        <v>58946</v>
       </c>
       <c r="M8" s="9">
         <f>+$L8</f>
+        <v>58946</v>
       </c>
       <c r="N8" s="9">
         <f>+$L8</f>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>58946</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="9">
         <f>'Data Sheet'!B27</f>
+        <v>3849</v>
       </c>
       <c r="C9" s="9">
         <f>'Data Sheet'!C27</f>
+        <v>8052</v>
       </c>
       <c r="D9" s="9">
         <f>'Data Sheet'!D27</f>
+        <v>16495</v>
       </c>
       <c r="E9" s="9">
         <f>'Data Sheet'!E27</f>
+        <v>22027</v>
       </c>
       <c r="F9" s="9">
         <f>'Data Sheet'!F27</f>
+        <v>21189</v>
       </c>
       <c r="G9" s="9">
         <f>'Data Sheet'!G27</f>
+        <v>14584</v>
       </c>
       <c r="H9" s="9">
         <f>'Data Sheet'!H27</f>
+        <v>19571</v>
       </c>
       <c r="I9" s="9">
         <f>'Data Sheet'!I27</f>
+        <v>23118</v>
       </c>
       <c r="J9" s="9">
         <f>'Data Sheet'!J27</f>
+        <v>24269</v>
       </c>
       <c r="K9" s="9">
         <f>'Data Sheet'!K27</f>
+        <v>27061</v>
       </c>
       <c r="L9" s="9">
         <f>SUM(Quarters!H9:K9)</f>
+        <v>28362</v>
       </c>
       <c r="M9" s="9">
         <f>+$L9</f>
+        <v>28362</v>
       </c>
       <c r="N9" s="9">
         <f>+$L9</f>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>28362</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="9">
         <f>'Data Sheet'!B28</f>
+        <v>40034</v>
       </c>
       <c r="C10" s="9">
         <f>'Data Sheet'!C28</f>
+        <v>49426</v>
       </c>
       <c r="D10" s="9">
         <f>'Data Sheet'!D28</f>
+        <v>55227</v>
       </c>
       <c r="E10" s="9">
         <f>'Data Sheet'!E28</f>
+        <v>53606</v>
       </c>
       <c r="F10" s="9">
         <f>'Data Sheet'!F28</f>
+        <v>55461</v>
       </c>
       <c r="G10" s="9">
         <f>'Data Sheet'!G28</f>
+        <v>83815</v>
       </c>
       <c r="H10" s="9">
         <f>'Data Sheet'!H28</f>
+        <v>94464</v>
       </c>
       <c r="I10" s="9">
         <f>'Data Sheet'!I28</f>
+        <v>104340</v>
       </c>
       <c r="J10" s="9">
         <f>'Data Sheet'!J28</f>
+        <v>106017</v>
       </c>
       <c r="K10" s="9">
         <f>'Data Sheet'!K28</f>
+        <v>123162</v>
       </c>
       <c r="L10" s="9">
         <f>SUM(Quarters!H10:K10)</f>
+        <v>116646</v>
       </c>
       <c r="M10" s="9">
         <f>M6+M7-SUM(M8:M9)</f>
+        <v>113932.67008501518</v>
       </c>
       <c r="N10" s="9">
         <f>N6+N7-SUM(N8:N9)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <v>97012.164998758381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="9">
         <f>'Data Sheet'!B29</f>
+        <v>10201</v>
       </c>
       <c r="C11" s="9">
         <f>'Data Sheet'!C29</f>
+        <v>13346</v>
       </c>
       <c r="D11" s="9">
         <f>'Data Sheet'!D29</f>
+        <v>15390</v>
       </c>
       <c r="E11" s="9">
         <f>'Data Sheet'!E29</f>
+        <v>13726</v>
       </c>
       <c r="F11" s="9">
         <f>'Data Sheet'!F29</f>
+        <v>1722</v>
       </c>
       <c r="G11" s="9">
         <f>'Data Sheet'!G29</f>
+        <v>15970</v>
       </c>
       <c r="H11" s="9">
         <f>'Data Sheet'!H29</f>
+        <v>20376</v>
       </c>
       <c r="I11" s="9">
         <f>'Data Sheet'!I29</f>
+        <v>25707</v>
       </c>
       <c r="J11" s="9">
         <f>'Data Sheet'!J29</f>
+        <v>25230</v>
       </c>
       <c r="K11" s="9">
         <f>'Data Sheet'!K29</f>
+        <v>27552</v>
       </c>
       <c r="L11" s="9">
         <f>SUM(Quarters!H11:K11)</f>
+        <v>28716</v>
       </c>
       <c r="M11" s="10">
         <f>IF($L10&gt;0,$L11/$L10,0)</f>
+        <v>0.24618075201892906</v>
       </c>
       <c r="N11" s="10">
         <f>IF($L10&gt;0,$L11/$L10,0)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>0.24618075201892906</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1">
         <f>'Data Sheet'!B30</f>
+        <v>29901</v>
       </c>
       <c r="C12" s="1">
         <f>'Data Sheet'!C30</f>
+        <v>36075</v>
       </c>
       <c r="D12" s="1">
         <f>'Data Sheet'!D30</f>
+        <v>39588</v>
       </c>
       <c r="E12" s="1">
         <f>'Data Sheet'!E30</f>
+        <v>39354</v>
       </c>
       <c r="F12" s="1">
         <f>'Data Sheet'!F30</f>
+        <v>49128</v>
       </c>
       <c r="G12" s="1">
         <f>'Data Sheet'!G30</f>
+        <v>60705</v>
       </c>
       <c r="H12" s="1">
         <f>'Data Sheet'!H30</f>
+        <v>66702</v>
       </c>
       <c r="I12" s="1">
         <f>'Data Sheet'!I30</f>
+        <v>69621</v>
       </c>
       <c r="J12" s="1">
         <f>'Data Sheet'!J30</f>
+        <v>69648</v>
       </c>
       <c r="K12" s="1">
         <f>'Data Sheet'!K30</f>
+        <v>80775</v>
       </c>
       <c r="L12" s="1">
         <f>SUM(Quarters!H12:K12)</f>
+        <v>74727</v>
       </c>
       <c r="M12" s="1">
         <f>M10-M11*M10</f>
+        <v>85884.639683961606</v>
       </c>
       <c r="N12" s="1">
         <f>N10-N11*N10</f>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <v>73129.63726437962</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="9">
         <f>IF('Data Sheet'!B93&gt;0,B12/'Data Sheet'!B93,0)</f>
+        <v>21.554620031429767</v>
       </c>
       <c r="C13" s="9">
         <f>IF('Data Sheet'!C93&gt;0,C12/'Data Sheet'!C93,0)</f>
+        <v>26.694736530535224</v>
       </c>
       <c r="D13" s="9">
         <f>IF('Data Sheet'!D93&gt;0,D12/'Data Sheet'!D93,0)</f>
+        <v>29.275435197373287</v>
       </c>
       <c r="E13" s="9">
         <f>IF('Data Sheet'!E93&gt;0,E12/'Data Sheet'!E93,0)</f>
+        <v>29.100024401606071</v>
       </c>
       <c r="F13" s="9">
         <f>IF('Data Sheet'!F93&gt;0,F12/'Data Sheet'!F93,0)</f>
+        <v>38.747840901024531</v>
       </c>
       <c r="G13" s="9">
         <f>IF('Data Sheet'!G93&gt;0,G12/'Data Sheet'!G93,0)</f>
+        <v>44.867625537701961</v>
       </c>
       <c r="H13" s="9">
         <f>IF('Data Sheet'!H93&gt;0,H12/'Data Sheet'!H93,0)</f>
+        <v>49.294962752749207</v>
       </c>
       <c r="I13" s="9">
         <f>IF('Data Sheet'!I93&gt;0,I12/'Data Sheet'!I93,0)</f>
+        <v>51.45143887550438</v>
       </c>
       <c r="J13" s="9">
         <f>IF('Data Sheet'!J93&gt;0,J12/'Data Sheet'!J93,0)</f>
+        <v>51.467588897756492</v>
       </c>
       <c r="K13" s="9">
         <f>IF('Data Sheet'!K93&gt;0,K12/'Data Sheet'!K93,0)</f>
+        <v>59.689636061333829</v>
       </c>
       <c r="L13" s="9">
         <f>IF('Data Sheet'!$B6&gt;0,'Profit &amp; Loss'!L12/'Data Sheet'!$B6,0)</f>
+        <v>55.220253972697613</v>
       </c>
       <c r="M13" s="9">
         <f>IF('Data Sheet'!$B6&gt;0,'Profit &amp; Loss'!M12/'Data Sheet'!$B6,0)</f>
+        <v>63.465301908306024</v>
       </c>
       <c r="N13" s="9">
         <f>IF('Data Sheet'!$B6&gt;0,'Profit &amp; Loss'!N12/'Data Sheet'!$B6,0)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+        <v>54.039867018216903</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="9" t="str">
+      <c r="B14" s="9">
         <f>IF(B15&gt;0,B15/B13,"")</f>
-      </c>
-      <c r="C14" s="9" t="str">
+        <v>13.92230526738236</v>
+      </c>
+      <c r="C14" s="9">
         <f t="shared" ref="C14:K14" si="2">IF(C15&gt;0,C15/C13,"")</f>
-      </c>
-      <c r="D14" s="9" t="str">
+        <v>15.02468471794872</v>
+      </c>
+      <c r="D14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="E14" s="9" t="str">
+        <v>21.158694851975344</v>
+      </c>
+      <c r="E14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="F14" s="9" t="str">
+        <v>17.390363424302485</v>
+      </c>
+      <c r="F14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="G14" s="9" t="str">
+        <v>23.71177280166097</v>
+      </c>
+      <c r="G14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="H14" s="9" t="str">
+        <v>26.935011280784121</v>
+      </c>
+      <c r="H14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="I14" s="9" t="str">
+        <v>21.690045803724026</v>
+      </c>
+      <c r="I14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="J14" s="9" t="str">
+        <v>28.87868701972106</v>
+      </c>
+      <c r="J14" s="9">
         <f t="shared" si="2"/>
-      </c>
-      <c r="K14" s="9" t="str">
+        <v>24.774815127498275</v>
+      </c>
+      <c r="K14" s="9">
         <f t="shared" si="2"/>
+        <v>22.514796347879912</v>
       </c>
       <c r="L14" s="9">
         <f t="shared" ref="L14" si="3">IF(L13&gt;0,L15/L13,0)</f>
+        <v>23.74400524576124</v>
       </c>
       <c r="M14" s="9">
         <f>M25</f>
+        <v>24.978075935215124</v>
       </c>
       <c r="N14" s="9">
         <f>N25</f>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>21.795016535330774</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
       <c r="B15" s="1">
         <f>'Data Sheet'!B90</f>
+        <v>300.08999999999997</v>
       </c>
       <c r="C15" s="1">
         <f>'Data Sheet'!C90</f>
+        <v>401.08</v>
       </c>
       <c r="D15" s="1">
         <f>'Data Sheet'!D90</f>
+        <v>619.42999999999995</v>
       </c>
       <c r="E15" s="1">
         <f>'Data Sheet'!E90</f>
+        <v>506.06</v>
       </c>
       <c r="F15" s="1">
         <f>'Data Sheet'!F90</f>
+        <v>918.78</v>
       </c>
       <c r="G15" s="1">
         <f>'Data Sheet'!G90</f>
+        <v>1208.51</v>
       </c>
       <c r="H15" s="1">
         <f>'Data Sheet'!H90</f>
+        <v>1069.21</v>
       </c>
       <c r="I15" s="1">
         <f>'Data Sheet'!I90</f>
+        <v>1485.85</v>
       </c>
       <c r="J15" s="1">
         <f>'Data Sheet'!J90</f>
+        <v>1275.0999999999999</v>
       </c>
       <c r="K15" s="1">
         <f>'Data Sheet'!K90</f>
+        <v>1343.9</v>
       </c>
       <c r="L15" s="1">
         <f>'Data Sheet'!B8</f>
+        <v>1311.15</v>
       </c>
       <c r="M15" s="12">
         <f>M13*M14</f>
+        <v>1585.2411303170211</v>
       </c>
       <c r="N15" s="13">
         <f>N13*N14</f>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>1177.7997952291134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="7">
         <f>IF('Data Sheet'!B30&gt;0, 'Data Sheet'!B31/'Data Sheet'!B30, 0)</f>
+        <v>0.10885589110732083</v>
       </c>
       <c r="C18" s="7">
         <f>IF('Data Sheet'!C30&gt;0, 'Data Sheet'!C31/'Data Sheet'!C30, 0)</f>
+        <v>9.8494802494802483E-2</v>
       </c>
       <c r="D18" s="7">
         <f>IF('Data Sheet'!D30&gt;0, 'Data Sheet'!D31/'Data Sheet'!D30, 0)</f>
+        <v>9.7299686773769836E-2</v>
       </c>
       <c r="E18" s="7">
         <f>IF('Data Sheet'!E30&gt;0, 'Data Sheet'!E31/'Data Sheet'!E30, 0)</f>
+        <v>0.10469964933678916</v>
       </c>
       <c r="F18" s="7">
         <f>IF('Data Sheet'!F30&gt;0, 'Data Sheet'!F31/'Data Sheet'!F30, 0)</f>
+        <v>9.1831542094121477E-2</v>
       </c>
       <c r="G18" s="7">
         <f>IF('Data Sheet'!G30&gt;0, 'Data Sheet'!G31/'Data Sheet'!G30, 0)</f>
+        <v>8.9152458611317029E-2</v>
       </c>
       <c r="H18" s="7">
         <f>IF('Data Sheet'!H30&gt;0, 'Data Sheet'!H31/'Data Sheet'!H30, 0)</f>
+        <v>9.129261491409553E-2</v>
       </c>
       <c r="I18" s="7">
         <f>IF('Data Sheet'!I30&gt;0, 'Data Sheet'!I31/'Data Sheet'!I30, 0)</f>
+        <v>9.718332112437339E-2</v>
       </c>
       <c r="J18" s="7">
         <f>IF('Data Sheet'!J30&gt;0, 'Data Sheet'!J31/'Data Sheet'!J30, 0)</f>
+        <v>0.1068602113484953</v>
       </c>
       <c r="K18" s="7">
         <f>IF('Data Sheet'!K30&gt;0, 'Data Sheet'!K31/'Data Sheet'!K30, 0)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.10051624883936862</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="7">
         <f t="shared" ref="B19:L19" si="4">IF(B6&gt;0,B6/B4,0)</f>
+        <v>0.15234871066016567</v>
       </c>
       <c r="C19" s="7">
         <f t="shared" ref="C19:K19" si="5">IF(C6&gt;0,C6/C4,0)</f>
+        <v>0.16456298631349742</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="5"/>
+        <v>0.14823951282425743</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="5"/>
+        <v>0.1496047288408005</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="5"/>
+        <v>0.17325495864312568</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="5"/>
+        <v>0.15630519683361813</v>
       </c>
       <c r="H19" s="7">
         <f t="shared" si="5"/>
+        <v>0.16239006111392568</v>
       </c>
       <c r="I19" s="7">
         <f t="shared" si="5"/>
+        <v>0.18074592816122959</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="5"/>
+        <v>0.17199268814524002</v>
       </c>
       <c r="K19" s="7">
         <f t="shared" si="5"/>
+        <v>0.16960446305101443</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="4"/>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.16344791662029018</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -2405,7 +2597,7 @@
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
@@ -2418,7 +2610,7 @@
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
     </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -2450,7 +2642,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -2460,78 +2652,99 @@
       <c r="G23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="7" t="str">
+      <c r="H23" s="7">
         <f>IF(B4=0,"",POWER($K4/B4,1/9)-1)</f>
-      </c>
-      <c r="I23" s="7" t="str">
+        <v>0.14837852661089657</v>
+      </c>
+      <c r="I23" s="7">
         <f>IF(D4=0,"",POWER($K4/D4,1/7)-1)</f>
-      </c>
-      <c r="J23" s="7" t="str">
+        <v>9.2506246101558443E-2</v>
+      </c>
+      <c r="J23" s="7">
         <f>IF(F4=0,"",POWER($K4/F4,1/5)-1)</f>
-      </c>
-      <c r="K23" s="7" t="str">
+        <v>0.17755255516198476</v>
+      </c>
+      <c r="K23" s="7">
         <f>IF(H4=0,"",POWER($K4/H4, 1/3)-1)</f>
-      </c>
-      <c r="L23" s="7" t="str">
+        <v>6.403933073685808E-2</v>
+      </c>
+      <c r="L23" s="7">
         <f>IF(ISERROR(MAX(IF(J4=0,"",(K4-J4)/J4),IF(K4=0,"",(L4-K4)/K4))),"",MAX(IF(J4=0,"",(K4-J4)/J4),IF(K4=0,"",(L4-K4)/K4)))</f>
+        <v>9.6549718535136372E-2</v>
       </c>
       <c r="M23" s="22">
         <f>MAX(K23:L23)</f>
+        <v>9.6549718535136372E-2</v>
       </c>
       <c r="N23" s="22">
         <f>MIN(H23:L23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+        <v>6.403933073685808E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G24" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="7" t="str">
+      <c r="H24" s="7">
         <f>IF(SUM(B4:$K$4)=0,"",SUMPRODUCT(B19:$K$19,B4:$K$4)/SUM(B4:$K$4))</f>
-      </c>
-      <c r="I24" s="7" t="str">
+        <v>0.16478639903386888</v>
+      </c>
+      <c r="I24" s="7">
         <f>IF(SUM(E4:$K$4)=0,"",SUMPRODUCT(E19:$K$19,E4:$K$4)/SUM(E4:$K$4))</f>
-      </c>
-      <c r="J24" s="7" t="str">
+        <v>0.16717702122018208</v>
+      </c>
+      <c r="J24" s="7">
         <f>IF(SUM(G4:$K$4)=0,"",SUMPRODUCT(G19:$K$19,G4:$K$4)/SUM(G4:$K$4))</f>
-      </c>
-      <c r="K24" s="7" t="str">
+        <v>0.16888148265314534</v>
+      </c>
+      <c r="K24" s="7">
         <f>IF(SUM(I4:$K$4)=0, "", SUMPRODUCT(I19:$K$19,I4:$K$4)/SUM(I4:$K$4))</f>
+        <v>0.17382570371063472</v>
       </c>
       <c r="L24" s="7">
         <f>L19</f>
+        <v>0.16344791662029018</v>
       </c>
       <c r="M24" s="22">
         <f>MAX(K24:L24)</f>
+        <v>0.17382570371063472</v>
       </c>
       <c r="N24" s="22">
         <f>MIN(H24:L24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.16344791662029018</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="9" t="str">
+      <c r="H25" s="9">
         <f>IF(ISERROR(AVERAGEIF(B14:$L14,"&gt;0")),"",AVERAGEIF(B14:$L14,"&gt;0"))</f>
-      </c>
-      <c r="I25" s="9" t="str">
+        <v>21.795016535330774</v>
+      </c>
+      <c r="I25" s="9">
         <f>IF(ISERROR(AVERAGEIF(E14:$L14,"&gt;0")),"",AVERAGEIF(E14:$L14,"&gt;0"))</f>
-      </c>
-      <c r="J25" s="9" t="str">
+        <v>23.704937131416511</v>
+      </c>
+      <c r="J25" s="9">
         <f>IF(ISERROR(AVERAGEIF(G14:$L14,"&gt;0")),"",AVERAGEIF(G14:$L14,"&gt;0"))</f>
-      </c>
-      <c r="K25" s="9" t="str">
+        <v>24.756226804228103</v>
+      </c>
+      <c r="K25" s="9">
         <f>IF(ISERROR(AVERAGEIF(I14:$L14,"&gt;0")),"",AVERAGEIF(I14:$L14,"&gt;0"))</f>
+        <v>24.978075935215124</v>
       </c>
       <c r="L25" s="9">
         <f>L14</f>
+        <v>23.74400524576124</v>
       </c>
       <c r="M25" s="1">
         <f>MAX(K25:L25)</f>
+        <v>24.978075935215124</v>
       </c>
       <c r="N25" s="1">
         <f>MIN(H25:L25)</f>
+        <v>21.795016535330774</v>
       </c>
     </row>
   </sheetData>
@@ -2553,411 +2766,523 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="6" customWidth="1"/>
-    <col min="2" max="11" width="13.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="6"/>
+    <col min="2" max="11" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="str">
         <f>'Profit &amp; Loss'!A1</f>
+        <v>RELIANCE INDUSTRIES LTD</v>
       </c>
       <c r="E1" t="str">
         <f>UPDATE</f>
+        <v/>
       </c>
       <c r="J1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="4"/>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16">
         <f>'Data Sheet'!B41</f>
+        <v>45382</v>
       </c>
       <c r="C3" s="16">
         <f>'Data Sheet'!C41</f>
+        <v>45473</v>
       </c>
       <c r="D3" s="16">
         <f>'Data Sheet'!D41</f>
+        <v>45565</v>
       </c>
       <c r="E3" s="16">
         <f>'Data Sheet'!E41</f>
+        <v>45657</v>
       </c>
       <c r="F3" s="16">
         <f>'Data Sheet'!F41</f>
+        <v>45747</v>
       </c>
       <c r="G3" s="16">
         <f>'Data Sheet'!G41</f>
+        <v>45838</v>
       </c>
       <c r="H3" s="16">
         <f>'Data Sheet'!H41</f>
+        <v>45930</v>
       </c>
       <c r="I3" s="16">
         <f>'Data Sheet'!I41</f>
+        <v>46022</v>
       </c>
       <c r="J3" s="16">
         <f>'Data Sheet'!J41</f>
+        <v>46112</v>
       </c>
       <c r="K3" s="16">
         <f>'Data Sheet'!K41</f>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1">
         <f>'Data Sheet'!B42</f>
+        <v>236533</v>
       </c>
       <c r="C4" s="1">
         <f>'Data Sheet'!C42</f>
+        <v>231784</v>
       </c>
       <c r="D4" s="1">
         <f>'Data Sheet'!D42</f>
+        <v>231535</v>
       </c>
       <c r="E4" s="1">
         <f>'Data Sheet'!E42</f>
+        <v>239986</v>
       </c>
       <c r="F4" s="1">
         <f>'Data Sheet'!F42</f>
+        <v>261388</v>
       </c>
       <c r="G4" s="1">
         <f>'Data Sheet'!G42</f>
+        <v>243632</v>
       </c>
       <c r="H4" s="1">
         <f>'Data Sheet'!H42</f>
+        <v>254623</v>
       </c>
       <c r="I4" s="1">
         <f>'Data Sheet'!I42</f>
+        <v>264905</v>
       </c>
       <c r="J4" s="1">
         <f>'Data Sheet'!J42</f>
+        <v>294059</v>
       </c>
       <c r="K4" s="1">
         <f>'Data Sheet'!K42</f>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>309468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="9">
         <f>'Data Sheet'!B43</f>
+        <v>194017</v>
       </c>
       <c r="C5" s="9">
         <f>'Data Sheet'!C43</f>
+        <v>193019</v>
       </c>
       <c r="D5" s="9">
         <f>'Data Sheet'!D43</f>
+        <v>192477</v>
       </c>
       <c r="E5" s="9">
         <f>'Data Sheet'!E43</f>
+        <v>196197</v>
       </c>
       <c r="F5" s="9">
         <f>'Data Sheet'!F43</f>
+        <v>217556</v>
       </c>
       <c r="G5" s="9">
         <f>'Data Sheet'!G43</f>
+        <v>200727</v>
       </c>
       <c r="H5" s="9">
         <f>'Data Sheet'!H43</f>
+        <v>208738</v>
       </c>
       <c r="I5" s="9">
         <f>'Data Sheet'!I43</f>
+        <v>218887</v>
       </c>
       <c r="J5" s="9">
         <f>'Data Sheet'!J43</f>
+        <v>249918</v>
       </c>
       <c r="K5" s="9">
         <f>'Data Sheet'!K43</f>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>261951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1">
         <f>'Data Sheet'!B50</f>
+        <v>42516</v>
       </c>
       <c r="C6" s="1">
         <f>'Data Sheet'!C50</f>
+        <v>38765</v>
       </c>
       <c r="D6" s="1">
         <f>'Data Sheet'!D50</f>
+        <v>39058</v>
       </c>
       <c r="E6" s="1">
         <f>'Data Sheet'!E50</f>
+        <v>43789</v>
       </c>
       <c r="F6" s="1">
         <f>'Data Sheet'!F50</f>
+        <v>43832</v>
       </c>
       <c r="G6" s="1">
         <f>'Data Sheet'!G50</f>
+        <v>42905</v>
       </c>
       <c r="H6" s="1">
         <f>'Data Sheet'!H50</f>
+        <v>45885</v>
       </c>
       <c r="I6" s="1">
         <f>'Data Sheet'!I50</f>
+        <v>46018</v>
       </c>
       <c r="J6" s="1">
         <f>'Data Sheet'!J50</f>
+        <v>44141</v>
       </c>
       <c r="K6" s="1">
         <f>'Data Sheet'!K50</f>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>47517</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="9">
         <f>'Data Sheet'!B44</f>
+        <v>4534</v>
       </c>
       <c r="C7" s="9">
         <f>'Data Sheet'!C44</f>
+        <v>3983</v>
       </c>
       <c r="D7" s="9">
         <f>'Data Sheet'!D44</f>
+        <v>4876</v>
       </c>
       <c r="E7" s="9">
         <f>'Data Sheet'!E44</f>
+        <v>4214</v>
       </c>
       <c r="F7" s="9">
         <f>'Data Sheet'!F44</f>
+        <v>4905</v>
       </c>
       <c r="G7" s="9">
         <f>'Data Sheet'!G44</f>
+        <v>15119</v>
       </c>
       <c r="H7" s="9">
         <f>'Data Sheet'!H44</f>
+        <v>4482</v>
       </c>
       <c r="I7" s="9">
         <f>'Data Sheet'!I44</f>
+        <v>4914</v>
       </c>
       <c r="J7" s="9">
         <f>'Data Sheet'!J44</f>
+        <v>4447</v>
       </c>
       <c r="K7" s="9">
         <f>'Data Sheet'!K44</f>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="9">
         <f>'Data Sheet'!B45</f>
+        <v>13569</v>
       </c>
       <c r="C8" s="9">
         <f>'Data Sheet'!C45</f>
+        <v>13596</v>
       </c>
       <c r="D8" s="9">
         <f>'Data Sheet'!D45</f>
+        <v>12880</v>
       </c>
       <c r="E8" s="9">
         <f>'Data Sheet'!E45</f>
+        <v>13181</v>
       </c>
       <c r="F8" s="9">
         <f>'Data Sheet'!F45</f>
+        <v>13479</v>
       </c>
       <c r="G8" s="9">
         <f>'Data Sheet'!G45</f>
+        <v>13842</v>
       </c>
       <c r="H8" s="9">
         <f>'Data Sheet'!H45</f>
+        <v>14416</v>
       </c>
       <c r="I8" s="9">
         <f>'Data Sheet'!I45</f>
+        <v>14622</v>
       </c>
       <c r="J8" s="9">
         <f>'Data Sheet'!J45</f>
+        <v>14808</v>
       </c>
       <c r="K8" s="9">
         <f>'Data Sheet'!K45</f>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="9">
         <f>'Data Sheet'!B46</f>
+        <v>5761</v>
       </c>
       <c r="C9" s="9">
         <f>'Data Sheet'!C46</f>
+        <v>5918</v>
       </c>
       <c r="D9" s="9">
         <f>'Data Sheet'!D46</f>
+        <v>6017</v>
       </c>
       <c r="E9" s="9">
         <f>'Data Sheet'!E46</f>
+        <v>6179</v>
       </c>
       <c r="F9" s="9">
         <f>'Data Sheet'!F46</f>
+        <v>6155</v>
       </c>
       <c r="G9" s="9">
         <f>'Data Sheet'!G46</f>
+        <v>7036</v>
       </c>
       <c r="H9" s="9">
         <f>'Data Sheet'!H46</f>
+        <v>6827</v>
       </c>
       <c r="I9" s="9">
         <f>'Data Sheet'!I46</f>
+        <v>6613</v>
       </c>
       <c r="J9" s="9">
         <f>'Data Sheet'!J46</f>
+        <v>6585</v>
       </c>
       <c r="K9" s="9">
         <f>'Data Sheet'!K46</f>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>8337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="9">
         <f>'Data Sheet'!B47</f>
+        <v>27720</v>
       </c>
       <c r="C10" s="9">
         <f>'Data Sheet'!C47</f>
+        <v>23234</v>
       </c>
       <c r="D10" s="9">
         <f>'Data Sheet'!D47</f>
+        <v>25037</v>
       </c>
       <c r="E10" s="9">
         <f>'Data Sheet'!E47</f>
+        <v>28643</v>
       </c>
       <c r="F10" s="9">
         <f>'Data Sheet'!F47</f>
+        <v>29103</v>
       </c>
       <c r="G10" s="9">
         <f>'Data Sheet'!G47</f>
+        <v>37146</v>
       </c>
       <c r="H10" s="9">
         <f>'Data Sheet'!H47</f>
+        <v>29124</v>
       </c>
       <c r="I10" s="9">
         <f>'Data Sheet'!I47</f>
+        <v>29697</v>
       </c>
       <c r="J10" s="9">
         <f>'Data Sheet'!J47</f>
+        <v>27195</v>
       </c>
       <c r="K10" s="9">
         <f>'Data Sheet'!K47</f>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>30630</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="9">
         <f>'Data Sheet'!B48</f>
+        <v>6577</v>
       </c>
       <c r="C11" s="9">
         <f>'Data Sheet'!C48</f>
+        <v>5786</v>
       </c>
       <c r="D11" s="9">
         <f>'Data Sheet'!D48</f>
+        <v>5936</v>
       </c>
       <c r="E11" s="9">
         <f>'Data Sheet'!E48</f>
+        <v>6839</v>
       </c>
       <c r="F11" s="9">
         <f>'Data Sheet'!F48</f>
+        <v>6669</v>
       </c>
       <c r="G11" s="9">
         <f>'Data Sheet'!G48</f>
+        <v>6465</v>
       </c>
       <c r="H11" s="9">
         <f>'Data Sheet'!H48</f>
+        <v>6978</v>
       </c>
       <c r="I11" s="9">
         <f>'Data Sheet'!I48</f>
+        <v>7530</v>
       </c>
       <c r="J11" s="9">
         <f>'Data Sheet'!J48</f>
+        <v>6579</v>
       </c>
       <c r="K11" s="9">
         <f>'Data Sheet'!K48</f>
-      </c>
-    </row>
-    <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>7629</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1">
         <f>'Data Sheet'!B49</f>
+        <v>18951</v>
       </c>
       <c r="C12" s="1">
         <f>'Data Sheet'!C49</f>
+        <v>15138</v>
       </c>
       <c r="D12" s="1">
         <f>'Data Sheet'!D49</f>
+        <v>16563</v>
       </c>
       <c r="E12" s="1">
         <f>'Data Sheet'!E49</f>
+        <v>18540</v>
       </c>
       <c r="F12" s="1">
         <f>'Data Sheet'!F49</f>
+        <v>19407</v>
       </c>
       <c r="G12" s="1">
         <f>'Data Sheet'!G49</f>
+        <v>26994</v>
       </c>
       <c r="H12" s="1">
         <f>'Data Sheet'!H49</f>
+        <v>18165</v>
       </c>
       <c r="I12" s="1">
         <f>'Data Sheet'!I49</f>
+        <v>18645</v>
       </c>
       <c r="J12" s="1">
         <f>'Data Sheet'!J49</f>
+        <v>16971</v>
       </c>
       <c r="K12" s="1">
         <f>'Data Sheet'!K49</f>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>20946</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="14" t="str">
+      <c r="B14" s="14">
         <f>IF(B4&gt;0,B6/B4,"")</f>
-      </c>
-      <c r="C14" s="14" t="str">
+        <v>0.17974658927084169</v>
+      </c>
+      <c r="C14" s="14">
         <f t="shared" ref="C14:K14" si="0">IF(C4&gt;0,C6/C4,"")</f>
-      </c>
-      <c r="D14" s="14" t="str">
+        <v>0.16724622924792049</v>
+      </c>
+      <c r="D14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="E14" s="14" t="str">
+        <v>0.16869155851167211</v>
+      </c>
+      <c r="E14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="F14" s="14" t="str">
+        <v>0.18246481044727608</v>
+      </c>
+      <c r="F14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="G14" s="14" t="str">
+        <v>0.16768941190873338</v>
+      </c>
+      <c r="G14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="H14" s="14" t="str">
+        <v>0.17610576607342221</v>
+      </c>
+      <c r="H14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="I14" s="14" t="str">
+        <v>0.18020760104153985</v>
+      </c>
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="J14" s="14" t="str">
+        <v>0.17371510541514884</v>
+      </c>
+      <c r="J14" s="14">
         <f t="shared" si="0"/>
-      </c>
-      <c r="K14" s="14" t="str">
+        <v>0.15010933180076108</v>
+      </c>
+      <c r="K14" s="14">
         <f t="shared" si="0"/>
-      </c>
-    </row>
-    <row r="22" s="30" customFormat="1" x14ac:dyDescent="0.2"/>
+        <v>0.15354414672922564</v>
+      </c>
+    </row>
+    <row r="22" s="30" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -2977,20 +3302,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="11" customWidth="1"/>
-    <col min="3" max="11" width="15.5" style="11" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="11"/>
+    <col min="1" max="1" width="22.77734375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" style="11" customWidth="1"/>
+    <col min="3" max="11" width="15.44140625" style="11" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="str">
         <f>'Profit &amp; Loss'!A1</f>
+        <v>RELIANCE INDUSTRIES LTD</v>
       </c>
       <c r="E1" t="str">
         <f>UPDATE</f>
+        <v/>
       </c>
       <c r="G1"/>
       <c r="J1" s="4" t="s">
@@ -2998,221 +3325,281 @@
       </c>
       <c r="K1" s="4"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16">
         <f>'Data Sheet'!B56</f>
+        <v>42825</v>
       </c>
       <c r="C3" s="16">
         <f>'Data Sheet'!C56</f>
+        <v>43190</v>
       </c>
       <c r="D3" s="16">
         <f>'Data Sheet'!D56</f>
+        <v>43555</v>
       </c>
       <c r="E3" s="16">
         <f>'Data Sheet'!E56</f>
+        <v>43921</v>
       </c>
       <c r="F3" s="16">
         <f>'Data Sheet'!F56</f>
+        <v>44286</v>
       </c>
       <c r="G3" s="16">
         <f>'Data Sheet'!G56</f>
+        <v>44651</v>
       </c>
       <c r="H3" s="16">
         <f>'Data Sheet'!H56</f>
+        <v>45016</v>
       </c>
       <c r="I3" s="16">
         <f>'Data Sheet'!I56</f>
+        <v>45382</v>
       </c>
       <c r="J3" s="16">
         <f>'Data Sheet'!J56</f>
+        <v>45747</v>
       </c>
       <c r="K3" s="16">
         <f>'Data Sheet'!K56</f>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="19">
         <f>'Data Sheet'!B57</f>
+        <v>2959</v>
       </c>
       <c r="C4" s="19">
         <f>'Data Sheet'!C57</f>
+        <v>5922</v>
       </c>
       <c r="D4" s="19">
         <f>'Data Sheet'!D57</f>
+        <v>5926</v>
       </c>
       <c r="E4" s="19">
         <f>'Data Sheet'!E57</f>
+        <v>6339</v>
       </c>
       <c r="F4" s="19">
         <f>'Data Sheet'!F57</f>
+        <v>6445</v>
       </c>
       <c r="G4" s="19">
         <f>'Data Sheet'!G57</f>
+        <v>6765</v>
       </c>
       <c r="H4" s="19">
         <f>'Data Sheet'!H57</f>
+        <v>6766</v>
       </c>
       <c r="I4" s="19">
         <f>'Data Sheet'!I57</f>
+        <v>6766</v>
       </c>
       <c r="J4" s="19">
         <f>'Data Sheet'!J57</f>
+        <v>13532</v>
       </c>
       <c r="K4" s="19">
         <f>'Data Sheet'!K57</f>
-      </c>
-    </row>
-    <row r="5" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>13532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="19">
         <f>'Data Sheet'!B58</f>
+        <v>260750</v>
       </c>
       <c r="C5" s="19">
         <f>'Data Sheet'!C58</f>
+        <v>287584</v>
       </c>
       <c r="D5" s="19">
         <f>'Data Sheet'!D58</f>
+        <v>381186</v>
       </c>
       <c r="E5" s="19">
         <f>'Data Sheet'!E58</f>
+        <v>442827</v>
       </c>
       <c r="F5" s="19">
         <f>'Data Sheet'!F58</f>
+        <v>693727</v>
       </c>
       <c r="G5" s="19">
         <f>'Data Sheet'!G58</f>
+        <v>772720</v>
       </c>
       <c r="H5" s="19">
         <f>'Data Sheet'!H58</f>
+        <v>709106</v>
       </c>
       <c r="I5" s="19">
         <f>'Data Sheet'!I58</f>
+        <v>786715</v>
       </c>
       <c r="J5" s="19">
         <f>'Data Sheet'!J58</f>
+        <v>829668</v>
       </c>
       <c r="K5" s="19">
         <f>'Data Sheet'!K58</f>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>890498</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B6" s="19">
         <f>'Data Sheet'!B59</f>
+        <v>217475</v>
       </c>
       <c r="C6" s="19">
         <f>'Data Sheet'!C59</f>
+        <v>239843</v>
       </c>
       <c r="D6" s="19">
         <f>'Data Sheet'!D59</f>
+        <v>307714</v>
       </c>
       <c r="E6" s="19">
         <f>'Data Sheet'!E59</f>
+        <v>355133</v>
       </c>
       <c r="F6" s="19">
         <f>'Data Sheet'!F59</f>
+        <v>278962</v>
       </c>
       <c r="G6" s="19">
         <f>'Data Sheet'!G59</f>
+        <v>319158</v>
       </c>
       <c r="H6" s="19">
         <f>'Data Sheet'!H59</f>
+        <v>451664</v>
       </c>
       <c r="I6" s="19">
         <f>'Data Sheet'!I59</f>
+        <v>350719</v>
       </c>
       <c r="J6" s="19">
         <f>'Data Sheet'!J59</f>
+        <v>374313</v>
       </c>
       <c r="K6" s="19">
         <f>'Data Sheet'!K59</f>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>402962</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B7" s="19">
         <f>'Data Sheet'!B60</f>
+        <v>225618</v>
       </c>
       <c r="C7" s="19">
         <f>'Data Sheet'!C60</f>
+        <v>277924</v>
       </c>
       <c r="D7" s="19">
         <f>'Data Sheet'!D60</f>
+        <v>302804</v>
       </c>
       <c r="E7" s="19">
         <f>'Data Sheet'!E60</f>
+        <v>358716</v>
       </c>
       <c r="F7" s="19">
         <f>'Data Sheet'!F60</f>
+        <v>340931</v>
       </c>
       <c r="G7" s="19">
         <f>'Data Sheet'!G60</f>
+        <v>399979</v>
       </c>
       <c r="H7" s="19">
         <f>'Data Sheet'!H60</f>
+        <v>438346</v>
       </c>
       <c r="I7" s="19">
         <f>'Data Sheet'!I60</f>
+        <v>610848</v>
       </c>
       <c r="J7" s="19">
         <f>'Data Sheet'!J60</f>
+        <v>732200</v>
       </c>
       <c r="K7" s="19">
         <f>'Data Sheet'!K60</f>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>870554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="20">
         <f>'Data Sheet'!B61</f>
+        <v>706802</v>
       </c>
       <c r="C8" s="20">
         <f>'Data Sheet'!C61</f>
+        <v>811273</v>
       </c>
       <c r="D8" s="20">
         <f>'Data Sheet'!D61</f>
+        <v>997630</v>
       </c>
       <c r="E8" s="20">
         <f>'Data Sheet'!E61</f>
+        <v>1163015</v>
       </c>
       <c r="F8" s="20">
         <f>'Data Sheet'!F61</f>
+        <v>1320065</v>
       </c>
       <c r="G8" s="20">
         <f>'Data Sheet'!G61</f>
+        <v>1498622</v>
       </c>
       <c r="H8" s="20">
         <f>'Data Sheet'!H61</f>
+        <v>1605882</v>
       </c>
       <c r="I8" s="20">
         <f>'Data Sheet'!I61</f>
+        <v>1755048</v>
       </c>
       <c r="J8" s="20">
         <f>'Data Sheet'!J61</f>
+        <v>1949713</v>
       </c>
       <c r="K8" s="20">
         <f>'Data Sheet'!K61</f>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>2177546</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
       <c r="D9" s="20"/>
@@ -3224,182 +3611,232 @@
       <c r="J9" s="20"/>
       <c r="K9" s="20"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="19">
         <f>'Data Sheet'!B62</f>
+        <v>198526</v>
       </c>
       <c r="C10" s="19">
         <f>'Data Sheet'!C62</f>
+        <v>403885</v>
       </c>
       <c r="D10" s="19">
         <f>'Data Sheet'!D62</f>
+        <v>398374</v>
       </c>
       <c r="E10" s="19">
         <f>'Data Sheet'!E62</f>
+        <v>532658</v>
       </c>
       <c r="F10" s="19">
         <f>'Data Sheet'!F62</f>
+        <v>541258</v>
       </c>
       <c r="G10" s="19">
         <f>'Data Sheet'!G62</f>
+        <v>627798</v>
       </c>
       <c r="H10" s="19">
         <f>'Data Sheet'!H62</f>
+        <v>724805</v>
       </c>
       <c r="I10" s="19">
         <f>'Data Sheet'!I62</f>
+        <v>779985</v>
       </c>
       <c r="J10" s="19">
         <f>'Data Sheet'!J62</f>
+        <v>999393</v>
       </c>
       <c r="K10" s="19">
         <f>'Data Sheet'!K62</f>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1124795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="19">
         <f>'Data Sheet'!B63</f>
+        <v>324837</v>
       </c>
       <c r="C11" s="19">
         <f>'Data Sheet'!C63</f>
+        <v>187022</v>
       </c>
       <c r="D11" s="19">
         <f>'Data Sheet'!D63</f>
+        <v>179463</v>
       </c>
       <c r="E11" s="19">
         <f>'Data Sheet'!E63</f>
+        <v>109106</v>
       </c>
       <c r="F11" s="19">
         <f>'Data Sheet'!F63</f>
+        <v>125953</v>
       </c>
       <c r="G11" s="19">
         <f>'Data Sheet'!G63</f>
+        <v>172506</v>
       </c>
       <c r="H11" s="19">
         <f>'Data Sheet'!H63</f>
+        <v>293752</v>
       </c>
       <c r="I11" s="19">
         <f>'Data Sheet'!I63</f>
+        <v>338855</v>
       </c>
       <c r="J11" s="19">
         <f>'Data Sheet'!J63</f>
+        <v>262358</v>
       </c>
       <c r="K11" s="19">
         <f>'Data Sheet'!K63</f>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>237686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="19">
         <f>'Data Sheet'!B64</f>
+        <v>82899</v>
       </c>
       <c r="C12" s="19">
         <f>'Data Sheet'!C64</f>
+        <v>82862</v>
       </c>
       <c r="D12" s="19">
         <f>'Data Sheet'!D64</f>
+        <v>235635</v>
       </c>
       <c r="E12" s="19">
         <f>'Data Sheet'!E64</f>
+        <v>276767</v>
       </c>
       <c r="F12" s="19">
         <f>'Data Sheet'!F64</f>
+        <v>364828</v>
       </c>
       <c r="G12" s="19">
         <f>'Data Sheet'!G64</f>
+        <v>394264</v>
       </c>
       <c r="H12" s="19">
         <f>'Data Sheet'!H64</f>
+        <v>235560</v>
       </c>
       <c r="I12" s="19">
         <f>'Data Sheet'!I64</f>
+        <v>225672</v>
       </c>
       <c r="J12" s="19">
         <f>'Data Sheet'!J64</f>
+        <v>242381</v>
       </c>
       <c r="K12" s="19">
         <f>'Data Sheet'!K64</f>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>248332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="19">
         <f>'Data Sheet'!B65</f>
+        <v>100540</v>
       </c>
       <c r="C13" s="19">
         <f>'Data Sheet'!C65</f>
+        <v>137504</v>
       </c>
       <c r="D13" s="19">
         <f>'Data Sheet'!D65</f>
+        <v>184158</v>
       </c>
       <c r="E13" s="19">
         <f>'Data Sheet'!E65</f>
+        <v>244484</v>
       </c>
       <c r="F13" s="19">
         <f>'Data Sheet'!F65</f>
+        <v>288026</v>
       </c>
       <c r="G13" s="19">
         <f>'Data Sheet'!G65</f>
+        <v>304054</v>
       </c>
       <c r="H13" s="19">
         <f>'Data Sheet'!H65</f>
+        <v>351765</v>
       </c>
       <c r="I13" s="19">
         <f>'Data Sheet'!I65</f>
+        <v>410536</v>
       </c>
       <c r="J13" s="19">
         <f>'Data Sheet'!J65</f>
+        <v>445581</v>
       </c>
       <c r="K13" s="19">
         <f>'Data Sheet'!K65</f>
-      </c>
-    </row>
-    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>566733</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="19">
         <f>'Data Sheet'!B66</f>
+        <v>706802</v>
       </c>
       <c r="C14" s="19">
         <f>'Data Sheet'!C66</f>
+        <v>811273</v>
       </c>
       <c r="D14" s="19">
         <f>'Data Sheet'!D66</f>
+        <v>997630</v>
       </c>
       <c r="E14" s="19">
         <f>'Data Sheet'!E66</f>
+        <v>1163015</v>
       </c>
       <c r="F14" s="19">
         <f>'Data Sheet'!F66</f>
+        <v>1320065</v>
       </c>
       <c r="G14" s="19">
         <f>'Data Sheet'!G66</f>
+        <v>1498622</v>
       </c>
       <c r="H14" s="19">
         <f>'Data Sheet'!H66</f>
+        <v>1605882</v>
       </c>
       <c r="I14" s="19">
         <f>'Data Sheet'!I66</f>
+        <v>1755048</v>
       </c>
       <c r="J14" s="19">
         <f>'Data Sheet'!J66</f>
+        <v>1949713</v>
       </c>
       <c r="K14" s="19">
         <f>'Data Sheet'!K66</f>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>2177546</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -3412,250 +3849,319 @@
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="21">
         <f>B13-B7</f>
+        <v>-125078</v>
       </c>
       <c r="C16" s="21">
         <f t="shared" ref="C16:K16" si="0">C13-C7</f>
+        <v>-140420</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
+        <v>-118646</v>
       </c>
       <c r="E16" s="21">
         <f t="shared" si="0"/>
+        <v>-114232</v>
       </c>
       <c r="F16" s="21">
         <f t="shared" si="0"/>
+        <v>-52905</v>
       </c>
       <c r="G16" s="21">
         <f t="shared" si="0"/>
+        <v>-95925</v>
       </c>
       <c r="H16" s="21">
         <f t="shared" si="0"/>
+        <v>-86581</v>
       </c>
       <c r="I16" s="21">
         <f t="shared" si="0"/>
+        <v>-200312</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="0"/>
+        <v>-286619</v>
       </c>
       <c r="K16" s="21">
         <f t="shared" si="0"/>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>-303821</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>44</v>
       </c>
       <c r="B17" s="21">
         <f>'Data Sheet'!B67</f>
+        <v>8177</v>
       </c>
       <c r="C17" s="21">
         <f>'Data Sheet'!C67</f>
+        <v>17555</v>
       </c>
       <c r="D17" s="21">
         <f>'Data Sheet'!D67</f>
+        <v>30089</v>
       </c>
       <c r="E17" s="21">
         <f>'Data Sheet'!E67</f>
+        <v>19656</v>
       </c>
       <c r="F17" s="21">
         <f>'Data Sheet'!F67</f>
+        <v>19014</v>
       </c>
       <c r="G17" s="21">
         <f>'Data Sheet'!G67</f>
+        <v>23640</v>
       </c>
       <c r="H17" s="21">
         <f>'Data Sheet'!H67</f>
+        <v>28448</v>
       </c>
       <c r="I17" s="21">
         <f>'Data Sheet'!I67</f>
+        <v>31628</v>
       </c>
       <c r="J17" s="21">
         <f>'Data Sheet'!J67</f>
+        <v>42121</v>
       </c>
       <c r="K17" s="21">
         <f>'Data Sheet'!K67</f>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>58491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="21">
         <f>'Data Sheet'!B68</f>
+        <v>48951</v>
       </c>
       <c r="C18" s="21">
         <f>'Data Sheet'!C68</f>
+        <v>60837</v>
       </c>
       <c r="D18" s="21">
         <f>'Data Sheet'!D68</f>
+        <v>67561</v>
       </c>
       <c r="E18" s="21">
         <f>'Data Sheet'!E68</f>
+        <v>73903</v>
       </c>
       <c r="F18" s="21">
         <f>'Data Sheet'!F68</f>
+        <v>81672</v>
       </c>
       <c r="G18" s="21">
         <f>'Data Sheet'!G68</f>
+        <v>107778</v>
       </c>
       <c r="H18" s="21">
         <f>'Data Sheet'!H68</f>
+        <v>140008</v>
       </c>
       <c r="I18" s="21">
         <f>'Data Sheet'!I68</f>
+        <v>152770</v>
       </c>
       <c r="J18" s="21">
         <f>'Data Sheet'!J68</f>
+        <v>146062</v>
       </c>
       <c r="K18" s="21">
         <f>'Data Sheet'!K68</f>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>166941</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B20" s="5">
         <f>IF('Profit &amp; Loss'!B4&gt;0,'Balance Sheet'!B17/('Profit &amp; Loss'!B4/365),0)</f>
+        <v>9.8192654151615049</v>
       </c>
       <c r="C20" s="5">
         <f>IF('Profit &amp; Loss'!C4&gt;0,'Balance Sheet'!C17/('Profit &amp; Loss'!C4/365),0)</f>
+        <v>16.395081661007669</v>
       </c>
       <c r="D20" s="5">
         <f>IF('Profit &amp; Loss'!D4&gt;0,'Balance Sheet'!D17/('Profit &amp; Loss'!D4/365),0)</f>
+        <v>19.323895857563382</v>
       </c>
       <c r="E20" s="5">
         <f>IF('Profit &amp; Loss'!E4&gt;0,'Balance Sheet'!E17/('Profit &amp; Loss'!E4/365),0)</f>
+        <v>12.023952577516555</v>
       </c>
       <c r="F20" s="5">
         <f>IF('Profit &amp; Loss'!F4&gt;0,'Balance Sheet'!F17/('Profit &amp; Loss'!F4/365),0)</f>
+        <v>14.883134930421376</v>
       </c>
       <c r="G20" s="5">
         <f>IF('Profit &amp; Loss'!G4&gt;0,'Balance Sheet'!G17/('Profit &amp; Loss'!G4/365),0)</f>
+        <v>12.421095968894717</v>
       </c>
       <c r="H20" s="5">
         <f>IF('Profit &amp; Loss'!H4&gt;0,'Balance Sheet'!H17/('Profit &amp; Loss'!H4/365),0)</f>
+        <v>11.847977398345039</v>
       </c>
       <c r="I20" s="5">
         <f>IF('Profit &amp; Loss'!I4&gt;0,'Balance Sheet'!I17/('Profit &amp; Loss'!I4/365),0)</f>
+        <v>12.840593476826974</v>
       </c>
       <c r="J20" s="5">
         <f>IF('Profit &amp; Loss'!J4&gt;0,'Balance Sheet'!J17/('Profit &amp; Loss'!J4/365),0)</f>
+        <v>15.967849649986498</v>
       </c>
       <c r="K20" s="5">
         <f>IF('Profit &amp; Loss'!K4&gt;0,'Balance Sheet'!K17/('Profit &amp; Loss'!K4/365),0)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20.221272424179279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>47</v>
       </c>
       <c r="B21" s="5">
         <f>IF('Balance Sheet'!B18&gt;0,'Profit &amp; Loss'!B4/'Balance Sheet'!B18,0)</f>
+        <v>6.2093522093522093</v>
       </c>
       <c r="C21" s="5">
         <f>IF('Balance Sheet'!C18&gt;0,'Profit &amp; Loss'!C4/'Balance Sheet'!C18,0)</f>
+        <v>6.4241004651774416</v>
       </c>
       <c r="D21" s="5">
         <f>IF('Balance Sheet'!D18&gt;0,'Profit &amp; Loss'!D4/'Balance Sheet'!D18,0)</f>
+        <v>8.41220526635189</v>
       </c>
       <c r="E21" s="5">
         <f>IF('Balance Sheet'!E18&gt;0,'Profit &amp; Loss'!E4/'Balance Sheet'!E18,0)</f>
+        <v>8.0738129710566557</v>
       </c>
       <c r="F21" s="5">
         <f>IF('Balance Sheet'!F18&gt;0,'Profit &amp; Loss'!F4/'Balance Sheet'!F18,0)</f>
+        <v>5.7095087667744151</v>
       </c>
       <c r="G21" s="5">
         <f>IF('Balance Sheet'!G18&gt;0,'Profit &amp; Loss'!G4/'Balance Sheet'!G18,0)</f>
+        <v>6.4454062981313438</v>
       </c>
       <c r="H21" s="5">
         <f>IF('Balance Sheet'!H18&gt;0,'Profit &amp; Loss'!H4/'Balance Sheet'!H18,0)</f>
+        <v>6.2596137363579221</v>
       </c>
       <c r="I21" s="5">
         <f>IF('Balance Sheet'!I18&gt;0,'Profit &amp; Loss'!I4/'Balance Sheet'!I18,0)</f>
+        <v>5.8849315965176405</v>
       </c>
       <c r="J21" s="5">
         <f>IF('Balance Sheet'!J18&gt;0,'Profit &amp; Loss'!J4/'Balance Sheet'!J18,0)</f>
+        <v>6.5918582519751885</v>
       </c>
       <c r="K21" s="5">
         <f>IF('Balance Sheet'!K18&gt;0,'Profit &amp; Loss'!K4/'Balance Sheet'!K18,0)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>6.3242702511665794</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="14" t="str">
+      <c r="B23" s="14">
         <f>IF(SUM('Balance Sheet'!B4:B5)&gt;0,'Profit &amp; Loss'!B12/SUM('Balance Sheet'!B4:B5),"")</f>
-      </c>
-      <c r="C23" s="14" t="str">
+        <v>0.11338634631355016</v>
+      </c>
+      <c r="C23" s="14">
         <f>IF(SUM('Balance Sheet'!C4:C5)&gt;0,'Profit &amp; Loss'!C12/SUM('Balance Sheet'!C4:C5),"")</f>
-      </c>
-      <c r="D23" s="14" t="str">
+        <v>0.12291060489393743</v>
+      </c>
+      <c r="D23" s="14">
         <f>IF(SUM('Balance Sheet'!D4:D5)&gt;0,'Profit &amp; Loss'!D12/SUM('Balance Sheet'!D4:D5),"")</f>
-      </c>
-      <c r="E23" s="14" t="str">
+        <v>0.10226497757754861</v>
+      </c>
+      <c r="E23" s="14">
         <f>IF(SUM('Balance Sheet'!E4:E5)&gt;0,'Profit &amp; Loss'!E12/SUM('Balance Sheet'!E4:E5),"")</f>
-      </c>
-      <c r="F23" s="14" t="str">
+        <v>8.7615714457461163E-2</v>
+      </c>
+      <c r="F23" s="14">
         <f>IF(SUM('Balance Sheet'!F4:F5)&gt;0,'Profit &amp; Loss'!F12/SUM('Balance Sheet'!F4:F5),"")</f>
-      </c>
-      <c r="G23" s="14" t="str">
+        <v>7.0165616448529797E-2</v>
+      </c>
+      <c r="G23" s="14">
         <f>IF(SUM('Balance Sheet'!G4:G5)&gt;0,'Profit &amp; Loss'!G12/SUM('Balance Sheet'!G4:G5),"")</f>
-      </c>
-      <c r="H23" s="14" t="str">
+        <v>7.787834275194519E-2</v>
+      </c>
+      <c r="H23" s="14">
         <f>IF(SUM('Balance Sheet'!H4:H5)&gt;0,'Profit &amp; Loss'!H12/SUM('Balance Sheet'!H4:H5),"")</f>
-      </c>
-      <c r="I23" s="14" t="str">
+        <v>9.3175875016762777E-2</v>
+      </c>
+      <c r="I23" s="14">
         <f>IF(SUM('Balance Sheet'!I4:I5)&gt;0,'Profit &amp; Loss'!I12/SUM('Balance Sheet'!I4:I5),"")</f>
-      </c>
-      <c r="J23" s="14" t="str">
+        <v>8.7741231359036956E-2</v>
+      </c>
+      <c r="J23" s="14">
         <f>IF(SUM('Balance Sheet'!J4:J5)&gt;0,'Profit &amp; Loss'!J12/SUM('Balance Sheet'!J4:J5),"")</f>
-      </c>
-      <c r="K23" s="14" t="str">
+        <v>8.259962049335863E-2</v>
+      </c>
+      <c r="K23" s="14">
         <f>IF(SUM('Balance Sheet'!K4:K5)&gt;0,'Profit &amp; Loss'!K12/SUM('Balance Sheet'!K4:K5),"")</f>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>8.9349910954282491E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>60</v>
       </c>
       <c r="B24" s="14"/>
-      <c r="C24" s="14" t="str">
+      <c r="C24" s="14">
         <f>IF((B4+B5+B6+C4+C5+C6)&gt;0,('Profit &amp; Loss'!C10+'Profit &amp; Loss'!C9)*2/(B4+B5+B6+C4+C5+C6),"")</f>
-      </c>
-      <c r="D24" s="14" t="str">
+        <v>0.1133092762877107</v>
+      </c>
+      <c r="D24" s="14">
         <f>IF((C4+C5+C6+D4+D5+D6)&gt;0,('Profit &amp; Loss'!D10+'Profit &amp; Loss'!D9)*2/(C4+C5+C6+D4+D5+D6),"")</f>
-      </c>
-      <c r="E24" s="14" t="str">
+        <v>0.11679443076108861</v>
+      </c>
+      <c r="E24" s="14">
         <f>IF((D4+D5+D6+E4+E5+E6)&gt;0,('Profit &amp; Loss'!E10+'Profit &amp; Loss'!E9)*2/(D4+D5+D6+E4+E5+E6),"")</f>
-      </c>
-      <c r="F24" s="14" t="str">
+        <v>0.10090286000166764</v>
+      </c>
+      <c r="F24" s="14">
         <f>IF((E4+E5+E6+F4+F5+F6)&gt;0,('Profit &amp; Loss'!F10+'Profit &amp; Loss'!F9)*2/(E4+E5+E6+F4+F5+F6),"")</f>
-      </c>
-      <c r="G24" s="14" t="str">
+        <v>8.5957812825040239E-2</v>
+      </c>
+      <c r="G24" s="14">
         <f>IF((F4+F5+F6+G4+G5+G6)&gt;0,('Profit &amp; Loss'!G10+'Profit &amp; Loss'!G9)*2/(F4+F5+F6+G4+G5+G6),"")</f>
-      </c>
-      <c r="H24" s="14" t="str">
+        <v>9.4715650428318338E-2</v>
+      </c>
+      <c r="H24" s="14">
         <f>IF((G4+G5+G6+H4+H5+H6)&gt;0,('Profit &amp; Loss'!H10+'Profit &amp; Loss'!H9)*2/(G4+G5+G6+H4+H5+H6),"")</f>
-      </c>
-      <c r="I24" s="14" t="str">
+        <v>0.10064077021276784</v>
+      </c>
+      <c r="I24" s="14">
         <f>IF((H4+H5+H6+I4+I5+I6)&gt;0,('Profit &amp; Loss'!I10+'Profit &amp; Loss'!I9)*2/(H4+H5+H6+I4+I5+I6),"")</f>
-      </c>
-      <c r="J24" s="14" t="str">
+        <v>0.11027037689424744</v>
+      </c>
+      <c r="J24" s="14">
         <f>IF((I4+I5+I6+J4+J5+J6)&gt;0,('Profit &amp; Loss'!J10+'Profit &amp; Loss'!J9)*2/(I4+I5+I6+J4+J5+J6),"")</f>
-      </c>
-      <c r="K24" s="14" t="str">
+        <v>0.11033178036450661</v>
+      </c>
+      <c r="K24" s="14">
         <f>IF((J4+J5+J6+K4+K5+K6)&gt;0,('Profit &amp; Loss'!K10+'Profit &amp; Loss'!K9)*2/(J4+J5+J6+K4+K5+K6),"")</f>
-      </c>
-    </row>
-    <row r="25" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.2"/>
+        <v>0.11901184588661935</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="18" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -3672,20 +4178,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="13.5" style="6" customWidth="1"/>
-    <col min="7" max="11" width="13.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="6"/>
+    <col min="1" max="1" width="26.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="13.44140625" style="6" customWidth="1"/>
+    <col min="7" max="11" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="str">
         <f>'Balance Sheet'!A1</f>
+        <v>RELIANCE INDUSTRIES LTD</v>
       </c>
       <c r="E1" t="str">
         <f>UPDATE</f>
+        <v/>
       </c>
       <c r="F1"/>
       <c r="J1" s="4" t="s">
@@ -3693,182 +4201,232 @@
       </c>
       <c r="K1" s="4"/>
     </row>
-    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="16">
         <f>'Data Sheet'!B81</f>
+        <v>42825</v>
       </c>
       <c r="C3" s="16">
         <f>'Data Sheet'!C81</f>
+        <v>43190</v>
       </c>
       <c r="D3" s="16">
         <f>'Data Sheet'!D81</f>
+        <v>43555</v>
       </c>
       <c r="E3" s="16">
         <f>'Data Sheet'!E81</f>
+        <v>43921</v>
       </c>
       <c r="F3" s="16">
         <f>'Data Sheet'!F81</f>
+        <v>44286</v>
       </c>
       <c r="G3" s="16">
         <f>'Data Sheet'!G81</f>
+        <v>44651</v>
       </c>
       <c r="H3" s="16">
         <f>'Data Sheet'!H81</f>
+        <v>45016</v>
       </c>
       <c r="I3" s="16">
         <f>'Data Sheet'!I81</f>
+        <v>45382</v>
       </c>
       <c r="J3" s="16">
         <f>'Data Sheet'!J81</f>
+        <v>45747</v>
       </c>
       <c r="K3" s="16">
         <f>'Data Sheet'!K81</f>
-      </c>
-    </row>
-    <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="1">
         <f>'Data Sheet'!B82</f>
+        <v>49550</v>
       </c>
       <c r="C4" s="1">
         <f>'Data Sheet'!C82</f>
+        <v>71459</v>
       </c>
       <c r="D4" s="1">
         <f>'Data Sheet'!D82</f>
+        <v>42346</v>
       </c>
       <c r="E4" s="1">
         <f>'Data Sheet'!E82</f>
+        <v>94877</v>
       </c>
       <c r="F4" s="1">
         <f>'Data Sheet'!F82</f>
+        <v>26958</v>
       </c>
       <c r="G4" s="1">
         <f>'Data Sheet'!G82</f>
+        <v>110654</v>
       </c>
       <c r="H4" s="1">
         <f>'Data Sheet'!H82</f>
+        <v>115032</v>
       </c>
       <c r="I4" s="1">
         <f>'Data Sheet'!I82</f>
+        <v>158788</v>
       </c>
       <c r="J4" s="1">
         <f>'Data Sheet'!J82</f>
+        <v>178703</v>
       </c>
       <c r="K4" s="1">
         <f>'Data Sheet'!K82</f>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>192113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="9">
         <f>'Data Sheet'!B83</f>
+        <v>-66201</v>
       </c>
       <c r="C5" s="9">
         <f>'Data Sheet'!C83</f>
+        <v>-68192</v>
       </c>
       <c r="D5" s="9">
         <f>'Data Sheet'!D83</f>
+        <v>-94507</v>
       </c>
       <c r="E5" s="9">
         <f>'Data Sheet'!E83</f>
+        <v>-72497</v>
       </c>
       <c r="F5" s="9">
         <f>'Data Sheet'!F83</f>
+        <v>-142385</v>
       </c>
       <c r="G5" s="9">
         <f>'Data Sheet'!G83</f>
+        <v>-109162</v>
       </c>
       <c r="H5" s="9">
         <f>'Data Sheet'!H83</f>
+        <v>-93001</v>
       </c>
       <c r="I5" s="9">
         <f>'Data Sheet'!I83</f>
+        <v>-113581</v>
       </c>
       <c r="J5" s="9">
         <f>'Data Sheet'!J83</f>
+        <v>-137535</v>
       </c>
       <c r="K5" s="9">
         <f>'Data Sheet'!K83</f>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>-101089</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="9">
         <f>'Data Sheet'!B84</f>
+        <v>8617</v>
       </c>
       <c r="C6" s="9">
         <f>'Data Sheet'!C84</f>
+        <v>-2001</v>
       </c>
       <c r="D6" s="9">
         <f>'Data Sheet'!D84</f>
+        <v>55906</v>
       </c>
       <c r="E6" s="9">
         <f>'Data Sheet'!E84</f>
+        <v>-2541</v>
       </c>
       <c r="F6" s="9">
         <f>'Data Sheet'!F84</f>
+        <v>101904</v>
       </c>
       <c r="G6" s="9">
         <f>'Data Sheet'!G84</f>
+        <v>17289</v>
       </c>
       <c r="H6" s="9">
         <f>'Data Sheet'!H84</f>
+        <v>10455</v>
       </c>
       <c r="I6" s="9">
         <f>'Data Sheet'!I84</f>
+        <v>-16646</v>
       </c>
       <c r="J6" s="9">
         <f>'Data Sheet'!J84</f>
+        <v>-31891</v>
       </c>
       <c r="K6" s="9">
         <f>'Data Sheet'!K84</f>
-      </c>
-    </row>
-    <row r="7" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+        <v>-51549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B7" s="1">
         <f>'Data Sheet'!B85</f>
+        <v>-8034</v>
       </c>
       <c r="C7" s="1">
         <f>'Data Sheet'!C85</f>
+        <v>1266</v>
       </c>
       <c r="D7" s="1">
         <f>'Data Sheet'!D85</f>
+        <v>3745</v>
       </c>
       <c r="E7" s="1">
         <f>'Data Sheet'!E85</f>
+        <v>19839</v>
       </c>
       <c r="F7" s="1">
         <f>'Data Sheet'!F85</f>
+        <v>-13523</v>
       </c>
       <c r="G7" s="1">
         <f>'Data Sheet'!G85</f>
+        <v>18781</v>
       </c>
       <c r="H7" s="1">
         <f>'Data Sheet'!H85</f>
+        <v>32486</v>
       </c>
       <c r="I7" s="1">
         <f>'Data Sheet'!I85</f>
+        <v>28561</v>
       </c>
       <c r="J7" s="1">
         <f>'Data Sheet'!J85</f>
+        <v>9277</v>
       </c>
       <c r="K7" s="1">
         <f>'Data Sheet'!K85</f>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>39475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="29"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -3881,7 +4439,7 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
     </row>
-    <row r="24" s="29" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="24" s="29" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="J1" r:id="rId1" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -3896,42 +4454,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="8"/>
-    <col min="2" max="2" width="10.5" style="11" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="8"/>
+    <col min="2" max="2" width="10.44140625" style="11" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" style="26" customWidth="1"/>
-    <col min="4" max="5" width="8.83203125" style="11"/>
-    <col min="6" max="6" width="6.83203125" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="11"/>
+    <col min="4" max="5" width="8.77734375" style="11"/>
+    <col min="6" max="6" width="6.77734375" style="11" customWidth="1"/>
+    <col min="7" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>51</v>
       </c>
@@ -3939,27 +4497,27 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
         <v>92</v>
       </c>
@@ -3976,14 +4534,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:K93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="11" width="13.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="5"/>
+    <col min="2" max="11" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.77734375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3992,6 +4550,7 @@
       </c>
       <c r="E1" s="32" t="str">
         <f>IF(B2&lt;&gt;B3, "A NEW VERSION OF THE WORKSHEET IS AVAILABLE", "")</f>
+        <v/>
       </c>
       <c r="F1" s="32"/>
       <c r="G1" s="32"/>
@@ -4000,7 +4559,7 @@
       <c r="J1" s="32"/>
       <c r="K1" s="32"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>61</v>
       </c>
@@ -4017,7 +4576,7 @@
       <c r="J2" s="33"/>
       <c r="K2" s="33"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>62</v>
       </c>
@@ -4025,31 +4584,32 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B6" s="5">
         <f>IF(B9&gt;0, B9/B8, 0)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1353.253464515883</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B7">
-        <v>10.00</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -4057,7 +4617,7 @@
         <v>1311.15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>79</v>
       </c>
@@ -4065,537 +4625,537 @@
         <v>1774318.28</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="16">
-        <v>42825.0</v>
+        <v>42825</v>
       </c>
       <c r="C16" s="16">
-        <v>43190.0</v>
+        <v>43190</v>
       </c>
       <c r="D16" s="16">
-        <v>43555.0</v>
+        <v>43555</v>
       </c>
       <c r="E16" s="16">
-        <v>43921.0</v>
+        <v>43921</v>
       </c>
       <c r="F16" s="16">
-        <v>44286.0</v>
+        <v>44286</v>
       </c>
       <c r="G16" s="16">
-        <v>44651.0</v>
+        <v>44651</v>
       </c>
       <c r="H16" s="16">
-        <v>45016.0</v>
+        <v>45016</v>
       </c>
       <c r="I16" s="16">
-        <v>45382.0</v>
+        <v>45382</v>
       </c>
       <c r="J16" s="16">
-        <v>45747.0</v>
+        <v>45747</v>
       </c>
       <c r="K16" s="16">
-        <v>46112.0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B17">
-        <v>303954.0</v>
+        <v>303954</v>
       </c>
       <c r="C17">
-        <v>390823.0</v>
+        <v>390823</v>
       </c>
       <c r="D17">
-        <v>568337.0</v>
+        <v>568337</v>
       </c>
       <c r="E17">
-        <v>596679.0</v>
+        <v>596679</v>
       </c>
       <c r="F17">
-        <v>466307.0</v>
+        <v>466307</v>
       </c>
       <c r="G17">
-        <v>694673.0</v>
+        <v>694673</v>
       </c>
       <c r="H17">
-        <v>876396.0</v>
+        <v>876396</v>
       </c>
       <c r="I17">
-        <v>899041.0</v>
+        <v>899041</v>
       </c>
       <c r="J17">
-        <v>962820.0</v>
+        <v>962820</v>
       </c>
       <c r="K17">
-        <v>1055780.0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>1055780</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B18">
-        <v>217518.0</v>
+        <v>217518</v>
       </c>
       <c r="C18">
-        <v>276076.0</v>
+        <v>276076</v>
       </c>
       <c r="D18">
-        <v>399167.0</v>
+        <v>399167</v>
       </c>
       <c r="E18">
-        <v>410288.0</v>
+        <v>410288</v>
       </c>
       <c r="F18">
-        <v>301765.0</v>
+        <v>301765</v>
       </c>
       <c r="G18">
-        <v>494449.0</v>
+        <v>494449</v>
       </c>
       <c r="H18">
-        <v>618746.0</v>
+        <v>618746</v>
       </c>
       <c r="I18">
-        <v>590226.0</v>
+        <v>590226</v>
       </c>
       <c r="J18">
-        <v>644813.0</v>
+        <v>644813</v>
       </c>
       <c r="K18">
-        <v>698930.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>698930</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B19">
-        <v>5218.0</v>
+        <v>5218</v>
       </c>
       <c r="C19">
-        <v>8610.0</v>
+        <v>8610</v>
       </c>
       <c r="D19">
-        <v>4680.0</v>
+        <v>4680</v>
       </c>
       <c r="E19">
-        <v>5048.0</v>
+        <v>5048</v>
       </c>
       <c r="F19">
-        <v>9064.0</v>
+        <v>9064</v>
       </c>
       <c r="G19">
-        <v>21457.0</v>
+        <v>21457</v>
       </c>
       <c r="H19">
-        <v>30263.0</v>
+        <v>30263</v>
       </c>
       <c r="I19">
-        <v>4883.0</v>
+        <v>4883</v>
       </c>
       <c r="J19">
-        <v>15124.0</v>
+        <v>15124</v>
       </c>
       <c r="K19">
-        <v>10267.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>10267</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B20">
-        <v>11251.0</v>
+        <v>11251</v>
       </c>
       <c r="C20">
-        <v>14569.0</v>
+        <v>14569</v>
       </c>
       <c r="D20">
-        <v>17029.0</v>
+        <v>17029</v>
       </c>
       <c r="E20">
-        <v>15098.0</v>
+        <v>15098</v>
       </c>
       <c r="F20">
-        <v>13214.0</v>
+        <v>13214</v>
       </c>
       <c r="G20">
-        <v>17902.0</v>
+        <v>17902</v>
       </c>
       <c r="H20">
-        <v>25062.0</v>
+        <v>25062</v>
       </c>
       <c r="I20">
-        <v>22137.0</v>
+        <v>22137</v>
       </c>
       <c r="J20">
-        <v>23823.0</v>
+        <v>23823</v>
       </c>
       <c r="K20">
-        <v>22069.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>22069</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B21">
-        <v>9909.0</v>
+        <v>9909</v>
       </c>
       <c r="C21">
-        <v>9691.0</v>
+        <v>9691</v>
       </c>
       <c r="D21">
-        <v>12198.0</v>
+        <v>12198</v>
       </c>
       <c r="E21">
-        <v>11434.0</v>
+        <v>11434</v>
       </c>
       <c r="F21">
-        <v>7687.0</v>
+        <v>7687</v>
       </c>
       <c r="G21">
-        <v>12174.0</v>
+        <v>12174</v>
       </c>
       <c r="H21">
-        <v>19658.0</v>
+        <v>19658</v>
       </c>
       <c r="I21">
-        <v>18276.0</v>
+        <v>18276</v>
       </c>
       <c r="J21">
-        <v>18358.0</v>
+        <v>18358</v>
       </c>
       <c r="K21">
-        <v>21162.0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>21162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B22">
-        <v>8388.0</v>
+        <v>8388</v>
       </c>
       <c r="C22">
-        <v>9523.0</v>
+        <v>9523</v>
       </c>
       <c r="D22">
-        <v>12488.0</v>
+        <v>12488</v>
       </c>
       <c r="E22">
-        <v>14075.0</v>
+        <v>14075</v>
       </c>
       <c r="F22">
-        <v>14817.0</v>
+        <v>14817</v>
       </c>
       <c r="G22">
-        <v>18758.0</v>
+        <v>18758</v>
       </c>
       <c r="H22">
-        <v>24872.0</v>
+        <v>24872</v>
       </c>
       <c r="I22">
-        <v>25679.0</v>
+        <v>25679</v>
       </c>
       <c r="J22">
-        <v>28559.0</v>
+        <v>28559</v>
       </c>
       <c r="K22">
-        <v>30318.0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>30318</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B23">
-        <v>18520.0</v>
+        <v>18520</v>
       </c>
       <c r="C23">
-        <v>29111.0</v>
+        <v>29111</v>
       </c>
       <c r="D23">
-        <v>50221.0</v>
+        <v>50221</v>
       </c>
       <c r="E23">
-        <v>62622.0</v>
+        <v>62622</v>
       </c>
       <c r="F23">
-        <v>56154.0</v>
+        <v>56154</v>
       </c>
       <c r="G23">
-        <v>63513.0</v>
+        <v>63513</v>
       </c>
       <c r="H23">
-        <v>67369.0</v>
+        <v>67369</v>
       </c>
       <c r="I23">
-        <v>77292.0</v>
+        <v>77292</v>
       </c>
       <c r="J23">
-        <v>88760.0</v>
+        <v>88760</v>
       </c>
       <c r="K23">
-        <v>104723.0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>104723</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B24">
-        <v>-2721.0</v>
+        <v>-2721</v>
       </c>
       <c r="C24">
-        <v>-3852.0</v>
+        <v>-3852</v>
       </c>
       <c r="D24">
-        <v>-2336.0</v>
+        <v>-2336</v>
       </c>
       <c r="E24">
-        <v>-1056.0</v>
+        <v>-1056</v>
       </c>
       <c r="F24">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="G24">
-        <v>753.0</v>
+        <v>753</v>
       </c>
       <c r="H24">
-        <v>8634.0</v>
+        <v>8634</v>
       </c>
       <c r="I24">
-        <v>7816.0</v>
+        <v>7816</v>
       </c>
       <c r="J24">
-        <v>8033.0</v>
+        <v>8033</v>
       </c>
       <c r="K24">
-        <v>9780.0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>9780</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B25">
-        <v>9222.0</v>
+        <v>9222</v>
       </c>
       <c r="C25">
-        <v>9869.0</v>
+        <v>9869</v>
       </c>
       <c r="D25">
-        <v>8406.0</v>
+        <v>8406</v>
       </c>
       <c r="E25">
-        <v>8570.0</v>
+        <v>8570</v>
       </c>
       <c r="F25">
-        <v>22432.0</v>
+        <v>22432</v>
       </c>
       <c r="G25">
-        <v>19600.0</v>
+        <v>19600</v>
       </c>
       <c r="H25">
-        <v>12020.0</v>
+        <v>12020</v>
       </c>
       <c r="I25">
-        <v>15792.0</v>
+        <v>15792</v>
       </c>
       <c r="J25">
-        <v>17824.0</v>
+        <v>17824</v>
       </c>
       <c r="K25">
-        <v>28846.0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>28846</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B26">
-        <v>11646.0</v>
+        <v>11646</v>
       </c>
       <c r="C26">
-        <v>16706.0</v>
+        <v>16706</v>
       </c>
       <c r="D26">
-        <v>20934.0</v>
+        <v>20934</v>
       </c>
       <c r="E26">
-        <v>22203.0</v>
+        <v>22203</v>
       </c>
       <c r="F26">
-        <v>26572.0</v>
+        <v>26572</v>
       </c>
       <c r="G26">
-        <v>29782.0</v>
+        <v>29782</v>
       </c>
       <c r="H26">
-        <v>40303.0</v>
+        <v>40303</v>
       </c>
       <c r="I26">
-        <v>50832.0</v>
+        <v>50832</v>
       </c>
       <c r="J26">
-        <v>53136.0</v>
+        <v>53136</v>
       </c>
       <c r="K26">
-        <v>57688.0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>57688</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B27">
-        <v>3849.0</v>
+        <v>3849</v>
       </c>
       <c r="C27">
-        <v>8052.0</v>
+        <v>8052</v>
       </c>
       <c r="D27">
-        <v>16495.0</v>
+        <v>16495</v>
       </c>
       <c r="E27">
-        <v>22027.0</v>
+        <v>22027</v>
       </c>
       <c r="F27">
-        <v>21189.0</v>
+        <v>21189</v>
       </c>
       <c r="G27">
-        <v>14584.0</v>
+        <v>14584</v>
       </c>
       <c r="H27">
-        <v>19571.0</v>
+        <v>19571</v>
       </c>
       <c r="I27">
-        <v>23118.0</v>
+        <v>23118</v>
       </c>
       <c r="J27">
-        <v>24269.0</v>
+        <v>24269</v>
       </c>
       <c r="K27">
-        <v>27061.0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>27061</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B28">
-        <v>40034.0</v>
+        <v>40034</v>
       </c>
       <c r="C28">
-        <v>49426.0</v>
+        <v>49426</v>
       </c>
       <c r="D28">
-        <v>55227.0</v>
+        <v>55227</v>
       </c>
       <c r="E28">
-        <v>53606.0</v>
+        <v>53606</v>
       </c>
       <c r="F28">
-        <v>55461.0</v>
+        <v>55461</v>
       </c>
       <c r="G28">
-        <v>83815.0</v>
+        <v>83815</v>
       </c>
       <c r="H28">
-        <v>94464.0</v>
+        <v>94464</v>
       </c>
       <c r="I28">
-        <v>104340.0</v>
+        <v>104340</v>
       </c>
       <c r="J28">
-        <v>106017.0</v>
+        <v>106017</v>
       </c>
       <c r="K28">
-        <v>123162.0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>123162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B29">
-        <v>10201.0</v>
+        <v>10201</v>
       </c>
       <c r="C29">
-        <v>13346.0</v>
+        <v>13346</v>
       </c>
       <c r="D29">
-        <v>15390.0</v>
+        <v>15390</v>
       </c>
       <c r="E29">
-        <v>13726.0</v>
+        <v>13726</v>
       </c>
       <c r="F29">
-        <v>1722.0</v>
+        <v>1722</v>
       </c>
       <c r="G29">
-        <v>15970.0</v>
+        <v>15970</v>
       </c>
       <c r="H29">
-        <v>20376.0</v>
+        <v>20376</v>
       </c>
       <c r="I29">
-        <v>25707.0</v>
+        <v>25707</v>
       </c>
       <c r="J29">
-        <v>25230.0</v>
+        <v>25230</v>
       </c>
       <c r="K29">
-        <v>27552.0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>27552</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B30">
-        <v>29901.0</v>
+        <v>29901</v>
       </c>
       <c r="C30">
-        <v>36075.0</v>
+        <v>36075</v>
       </c>
       <c r="D30">
-        <v>39588.0</v>
+        <v>39588</v>
       </c>
       <c r="E30">
-        <v>39354.0</v>
+        <v>39354</v>
       </c>
       <c r="F30">
-        <v>49128.0</v>
+        <v>49128</v>
       </c>
       <c r="G30">
-        <v>60705.0</v>
+        <v>60705</v>
       </c>
       <c r="H30">
-        <v>66702.0</v>
+        <v>66702</v>
       </c>
       <c r="I30">
-        <v>69621.0</v>
+        <v>69621</v>
       </c>
       <c r="J30">
-        <v>69648.0</v>
+        <v>69648</v>
       </c>
       <c r="K30">
-        <v>80775.0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>80775</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>70</v>
       </c>
@@ -4609,19 +5169,19 @@
         <v>3851.9</v>
       </c>
       <c r="E31">
-        <v>4120.35</v>
+        <v>4120.3500000000004</v>
       </c>
       <c r="F31">
         <v>4511.5</v>
       </c>
       <c r="G31">
-        <v>5412.0</v>
+        <v>5412</v>
       </c>
       <c r="H31">
         <v>6089.4</v>
       </c>
       <c r="I31">
-        <v>6766.0</v>
+        <v>6766</v>
       </c>
       <c r="J31">
         <v>7442.6</v>
@@ -4630,1199 +5190,1199 @@
         <v>8119.2</v>
       </c>
     </row>
-    <row r="32" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B41" s="16">
-        <v>45382.0</v>
+        <v>45382</v>
       </c>
       <c r="C41" s="16">
-        <v>45473.0</v>
+        <v>45473</v>
       </c>
       <c r="D41" s="16">
-        <v>45565.0</v>
+        <v>45565</v>
       </c>
       <c r="E41" s="16">
-        <v>45657.0</v>
+        <v>45657</v>
       </c>
       <c r="F41" s="16">
-        <v>45747.0</v>
+        <v>45747</v>
       </c>
       <c r="G41" s="16">
-        <v>45838.0</v>
+        <v>45838</v>
       </c>
       <c r="H41" s="16">
-        <v>45930.0</v>
+        <v>45930</v>
       </c>
       <c r="I41" s="16">
-        <v>46022.0</v>
+        <v>46022</v>
       </c>
       <c r="J41" s="16">
-        <v>46112.0</v>
+        <v>46112</v>
       </c>
       <c r="K41" s="16">
-        <v>46203.0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B42">
-        <v>236533.0</v>
+        <v>236533</v>
       </c>
       <c r="C42">
-        <v>231784.0</v>
+        <v>231784</v>
       </c>
       <c r="D42">
-        <v>231535.0</v>
+        <v>231535</v>
       </c>
       <c r="E42">
-        <v>239986.0</v>
+        <v>239986</v>
       </c>
       <c r="F42">
-        <v>261388.0</v>
+        <v>261388</v>
       </c>
       <c r="G42">
-        <v>243632.0</v>
+        <v>243632</v>
       </c>
       <c r="H42">
-        <v>254623.0</v>
+        <v>254623</v>
       </c>
       <c r="I42">
-        <v>264905.0</v>
+        <v>264905</v>
       </c>
       <c r="J42">
-        <v>294059.0</v>
+        <v>294059</v>
       </c>
       <c r="K42">
-        <v>309468.0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>309468</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B43">
-        <v>194017.0</v>
+        <v>194017</v>
       </c>
       <c r="C43">
-        <v>193019.0</v>
+        <v>193019</v>
       </c>
       <c r="D43">
-        <v>192477.0</v>
+        <v>192477</v>
       </c>
       <c r="E43">
-        <v>196197.0</v>
+        <v>196197</v>
       </c>
       <c r="F43">
-        <v>217556.0</v>
+        <v>217556</v>
       </c>
       <c r="G43">
-        <v>200727.0</v>
+        <v>200727</v>
       </c>
       <c r="H43">
-        <v>208738.0</v>
+        <v>208738</v>
       </c>
       <c r="I43">
-        <v>218887.0</v>
+        <v>218887</v>
       </c>
       <c r="J43">
-        <v>249918.0</v>
+        <v>249918</v>
       </c>
       <c r="K43">
-        <v>261951.0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>261951</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B44">
-        <v>4534.0</v>
+        <v>4534</v>
       </c>
       <c r="C44">
-        <v>3983.0</v>
+        <v>3983</v>
       </c>
       <c r="D44">
-        <v>4876.0</v>
+        <v>4876</v>
       </c>
       <c r="E44">
-        <v>4214.0</v>
+        <v>4214</v>
       </c>
       <c r="F44">
-        <v>4905.0</v>
+        <v>4905</v>
       </c>
       <c r="G44">
-        <v>15119.0</v>
+        <v>15119</v>
       </c>
       <c r="H44">
-        <v>4482.0</v>
+        <v>4482</v>
       </c>
       <c r="I44">
-        <v>4914.0</v>
+        <v>4914</v>
       </c>
       <c r="J44">
-        <v>4447.0</v>
+        <v>4447</v>
       </c>
       <c r="K44">
-        <v>6550.0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B45">
-        <v>13569.0</v>
+        <v>13569</v>
       </c>
       <c r="C45">
-        <v>13596.0</v>
+        <v>13596</v>
       </c>
       <c r="D45">
-        <v>12880.0</v>
+        <v>12880</v>
       </c>
       <c r="E45">
-        <v>13181.0</v>
+        <v>13181</v>
       </c>
       <c r="F45">
-        <v>13479.0</v>
+        <v>13479</v>
       </c>
       <c r="G45">
-        <v>13842.0</v>
+        <v>13842</v>
       </c>
       <c r="H45">
-        <v>14416.0</v>
+        <v>14416</v>
       </c>
       <c r="I45">
-        <v>14622.0</v>
+        <v>14622</v>
       </c>
       <c r="J45">
-        <v>14808.0</v>
+        <v>14808</v>
       </c>
       <c r="K45">
-        <v>15100.0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B46">
-        <v>5761.0</v>
+        <v>5761</v>
       </c>
       <c r="C46">
-        <v>5918.0</v>
+        <v>5918</v>
       </c>
       <c r="D46">
-        <v>6017.0</v>
+        <v>6017</v>
       </c>
       <c r="E46">
-        <v>6179.0</v>
+        <v>6179</v>
       </c>
       <c r="F46">
-        <v>6155.0</v>
+        <v>6155</v>
       </c>
       <c r="G46">
-        <v>7036.0</v>
+        <v>7036</v>
       </c>
       <c r="H46">
-        <v>6827.0</v>
+        <v>6827</v>
       </c>
       <c r="I46">
-        <v>6613.0</v>
+        <v>6613</v>
       </c>
       <c r="J46">
-        <v>6585.0</v>
+        <v>6585</v>
       </c>
       <c r="K46">
-        <v>8337.0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>8337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B47">
-        <v>27720.0</v>
+        <v>27720</v>
       </c>
       <c r="C47">
-        <v>23234.0</v>
+        <v>23234</v>
       </c>
       <c r="D47">
-        <v>25037.0</v>
+        <v>25037</v>
       </c>
       <c r="E47">
-        <v>28643.0</v>
+        <v>28643</v>
       </c>
       <c r="F47">
-        <v>29103.0</v>
+        <v>29103</v>
       </c>
       <c r="G47">
-        <v>37146.0</v>
+        <v>37146</v>
       </c>
       <c r="H47">
-        <v>29124.0</v>
+        <v>29124</v>
       </c>
       <c r="I47">
-        <v>29697.0</v>
+        <v>29697</v>
       </c>
       <c r="J47">
-        <v>27195.0</v>
+        <v>27195</v>
       </c>
       <c r="K47">
-        <v>30630.0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>30630</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B48">
-        <v>6577.0</v>
+        <v>6577</v>
       </c>
       <c r="C48">
-        <v>5786.0</v>
+        <v>5786</v>
       </c>
       <c r="D48">
-        <v>5936.0</v>
+        <v>5936</v>
       </c>
       <c r="E48">
-        <v>6839.0</v>
+        <v>6839</v>
       </c>
       <c r="F48">
-        <v>6669.0</v>
+        <v>6669</v>
       </c>
       <c r="G48">
-        <v>6465.0</v>
+        <v>6465</v>
       </c>
       <c r="H48">
-        <v>6978.0</v>
+        <v>6978</v>
       </c>
       <c r="I48">
-        <v>7530.0</v>
+        <v>7530</v>
       </c>
       <c r="J48">
-        <v>6579.0</v>
+        <v>6579</v>
       </c>
       <c r="K48">
-        <v>7629.0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>7629</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B49">
-        <v>18951.0</v>
+        <v>18951</v>
       </c>
       <c r="C49">
-        <v>15138.0</v>
+        <v>15138</v>
       </c>
       <c r="D49">
-        <v>16563.0</v>
+        <v>16563</v>
       </c>
       <c r="E49">
-        <v>18540.0</v>
+        <v>18540</v>
       </c>
       <c r="F49">
-        <v>19407.0</v>
+        <v>19407</v>
       </c>
       <c r="G49">
-        <v>26994.0</v>
+        <v>26994</v>
       </c>
       <c r="H49">
-        <v>18165.0</v>
+        <v>18165</v>
       </c>
       <c r="I49">
-        <v>18645.0</v>
+        <v>18645</v>
       </c>
       <c r="J49">
-        <v>16971.0</v>
+        <v>16971</v>
       </c>
       <c r="K49">
-        <v>20946.0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20946</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B50">
-        <v>42516.0</v>
+        <v>42516</v>
       </c>
       <c r="C50">
-        <v>38765.0</v>
+        <v>38765</v>
       </c>
       <c r="D50">
-        <v>39058.0</v>
+        <v>39058</v>
       </c>
       <c r="E50">
-        <v>43789.0</v>
+        <v>43789</v>
       </c>
       <c r="F50">
-        <v>43832.0</v>
+        <v>43832</v>
       </c>
       <c r="G50">
-        <v>42905.0</v>
+        <v>42905</v>
       </c>
       <c r="H50">
-        <v>45885.0</v>
+        <v>45885</v>
       </c>
       <c r="I50">
-        <v>46018.0</v>
+        <v>46018</v>
       </c>
       <c r="J50">
-        <v>44141.0</v>
+        <v>44141</v>
       </c>
       <c r="K50">
-        <v>47517.0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+        <v>47517</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B56" s="16">
-        <v>42825.0</v>
+        <v>42825</v>
       </c>
       <c r="C56" s="16">
-        <v>43190.0</v>
+        <v>43190</v>
       </c>
       <c r="D56" s="16">
-        <v>43555.0</v>
+        <v>43555</v>
       </c>
       <c r="E56" s="16">
-        <v>43921.0</v>
+        <v>43921</v>
       </c>
       <c r="F56" s="16">
-        <v>44286.0</v>
+        <v>44286</v>
       </c>
       <c r="G56" s="16">
-        <v>44651.0</v>
+        <v>44651</v>
       </c>
       <c r="H56" s="16">
-        <v>45016.0</v>
+        <v>45016</v>
       </c>
       <c r="I56" s="16">
-        <v>45382.0</v>
+        <v>45382</v>
       </c>
       <c r="J56" s="16">
-        <v>45747.0</v>
+        <v>45747</v>
       </c>
       <c r="K56" s="16">
-        <v>46112.0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B57">
-        <v>2959.0</v>
+        <v>2959</v>
       </c>
       <c r="C57">
-        <v>5922.0</v>
+        <v>5922</v>
       </c>
       <c r="D57">
-        <v>5926.0</v>
+        <v>5926</v>
       </c>
       <c r="E57">
-        <v>6339.0</v>
+        <v>6339</v>
       </c>
       <c r="F57">
-        <v>6445.0</v>
+        <v>6445</v>
       </c>
       <c r="G57">
-        <v>6765.0</v>
+        <v>6765</v>
       </c>
       <c r="H57">
-        <v>6766.0</v>
+        <v>6766</v>
       </c>
       <c r="I57">
-        <v>6766.0</v>
+        <v>6766</v>
       </c>
       <c r="J57">
-        <v>13532.0</v>
+        <v>13532</v>
       </c>
       <c r="K57">
-        <v>13532.0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+        <v>13532</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B58">
-        <v>260750.0</v>
+        <v>260750</v>
       </c>
       <c r="C58">
-        <v>287584.0</v>
+        <v>287584</v>
       </c>
       <c r="D58">
-        <v>381186.0</v>
+        <v>381186</v>
       </c>
       <c r="E58">
-        <v>442827.0</v>
+        <v>442827</v>
       </c>
       <c r="F58">
-        <v>693727.0</v>
+        <v>693727</v>
       </c>
       <c r="G58">
-        <v>772720.0</v>
+        <v>772720</v>
       </c>
       <c r="H58">
-        <v>709106.0</v>
+        <v>709106</v>
       </c>
       <c r="I58">
-        <v>786715.0</v>
+        <v>786715</v>
       </c>
       <c r="J58">
-        <v>829668.0</v>
+        <v>829668</v>
       </c>
       <c r="K58">
-        <v>890498.0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+        <v>890498</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="9" t="s">
         <v>71</v>
       </c>
       <c r="B59">
-        <v>217475.0</v>
+        <v>217475</v>
       </c>
       <c r="C59">
-        <v>239843.0</v>
+        <v>239843</v>
       </c>
       <c r="D59">
-        <v>307714.0</v>
+        <v>307714</v>
       </c>
       <c r="E59">
-        <v>355133.0</v>
+        <v>355133</v>
       </c>
       <c r="F59">
-        <v>278962.0</v>
+        <v>278962</v>
       </c>
       <c r="G59">
-        <v>319158.0</v>
+        <v>319158</v>
       </c>
       <c r="H59">
-        <v>451664.0</v>
+        <v>451664</v>
       </c>
       <c r="I59">
-        <v>350719.0</v>
+        <v>350719</v>
       </c>
       <c r="J59">
-        <v>374313.0</v>
+        <v>374313</v>
       </c>
       <c r="K59">
-        <v>402962.0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+        <v>402962</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="s">
         <v>72</v>
       </c>
       <c r="B60">
-        <v>225618.0</v>
+        <v>225618</v>
       </c>
       <c r="C60">
-        <v>277924.0</v>
+        <v>277924</v>
       </c>
       <c r="D60">
-        <v>302804.0</v>
+        <v>302804</v>
       </c>
       <c r="E60">
-        <v>358716.0</v>
+        <v>358716</v>
       </c>
       <c r="F60">
-        <v>340931.0</v>
+        <v>340931</v>
       </c>
       <c r="G60">
-        <v>399979.0</v>
+        <v>399979</v>
       </c>
       <c r="H60">
-        <v>438346.0</v>
+        <v>438346</v>
       </c>
       <c r="I60">
-        <v>610848.0</v>
+        <v>610848</v>
       </c>
       <c r="J60">
-        <v>732200.0</v>
+        <v>732200</v>
       </c>
       <c r="K60">
-        <v>870554.0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>870554</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B61">
-        <v>706802.0</v>
+        <v>706802</v>
       </c>
       <c r="C61">
-        <v>811273.0</v>
+        <v>811273</v>
       </c>
       <c r="D61">
-        <v>997630.0</v>
+        <v>997630</v>
       </c>
       <c r="E61">
-        <v>1163015.0</v>
+        <v>1163015</v>
       </c>
       <c r="F61">
-        <v>1320065.0</v>
+        <v>1320065</v>
       </c>
       <c r="G61">
-        <v>1498622.0</v>
+        <v>1498622</v>
       </c>
       <c r="H61">
-        <v>1605882.0</v>
+        <v>1605882</v>
       </c>
       <c r="I61">
-        <v>1755048.0</v>
+        <v>1755048</v>
       </c>
       <c r="J61">
-        <v>1949713.0</v>
+        <v>1949713</v>
       </c>
       <c r="K61">
-        <v>2177546.0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+        <v>2177546</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B62">
-        <v>198526.0</v>
+        <v>198526</v>
       </c>
       <c r="C62">
-        <v>403885.0</v>
+        <v>403885</v>
       </c>
       <c r="D62">
-        <v>398374.0</v>
+        <v>398374</v>
       </c>
       <c r="E62">
-        <v>532658.0</v>
+        <v>532658</v>
       </c>
       <c r="F62">
-        <v>541258.0</v>
+        <v>541258</v>
       </c>
       <c r="G62">
-        <v>627798.0</v>
+        <v>627798</v>
       </c>
       <c r="H62">
-        <v>724805.0</v>
+        <v>724805</v>
       </c>
       <c r="I62">
-        <v>779985.0</v>
+        <v>779985</v>
       </c>
       <c r="J62">
-        <v>999393.0</v>
+        <v>999393</v>
       </c>
       <c r="K62">
-        <v>1124795.0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1124795</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B63">
-        <v>324837.0</v>
+        <v>324837</v>
       </c>
       <c r="C63">
-        <v>187022.0</v>
+        <v>187022</v>
       </c>
       <c r="D63">
-        <v>179463.0</v>
+        <v>179463</v>
       </c>
       <c r="E63">
-        <v>109106.0</v>
+        <v>109106</v>
       </c>
       <c r="F63">
-        <v>125953.0</v>
+        <v>125953</v>
       </c>
       <c r="G63">
-        <v>172506.0</v>
+        <v>172506</v>
       </c>
       <c r="H63">
-        <v>293752.0</v>
+        <v>293752</v>
       </c>
       <c r="I63">
-        <v>338855.0</v>
+        <v>338855</v>
       </c>
       <c r="J63">
-        <v>262358.0</v>
+        <v>262358</v>
       </c>
       <c r="K63">
-        <v>237686.0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+        <v>237686</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B64">
-        <v>82899.0</v>
+        <v>82899</v>
       </c>
       <c r="C64">
-        <v>82862.0</v>
+        <v>82862</v>
       </c>
       <c r="D64">
-        <v>235635.0</v>
+        <v>235635</v>
       </c>
       <c r="E64">
-        <v>276767.0</v>
+        <v>276767</v>
       </c>
       <c r="F64">
-        <v>364828.0</v>
+        <v>364828</v>
       </c>
       <c r="G64">
-        <v>394264.0</v>
+        <v>394264</v>
       </c>
       <c r="H64">
-        <v>235560.0</v>
+        <v>235560</v>
       </c>
       <c r="I64">
-        <v>225672.0</v>
+        <v>225672</v>
       </c>
       <c r="J64">
-        <v>242381.0</v>
+        <v>242381</v>
       </c>
       <c r="K64">
-        <v>248332.0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+        <v>248332</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="s">
         <v>73</v>
       </c>
       <c r="B65">
-        <v>100540.0</v>
+        <v>100540</v>
       </c>
       <c r="C65">
-        <v>137504.0</v>
+        <v>137504</v>
       </c>
       <c r="D65">
-        <v>184158.0</v>
+        <v>184158</v>
       </c>
       <c r="E65">
-        <v>244484.0</v>
+        <v>244484</v>
       </c>
       <c r="F65">
-        <v>288026.0</v>
+        <v>288026</v>
       </c>
       <c r="G65">
-        <v>304054.0</v>
+        <v>304054</v>
       </c>
       <c r="H65">
-        <v>351765.0</v>
+        <v>351765</v>
       </c>
       <c r="I65">
-        <v>410536.0</v>
+        <v>410536</v>
       </c>
       <c r="J65">
-        <v>445581.0</v>
+        <v>445581</v>
       </c>
       <c r="K65">
-        <v>566733.0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>566733</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B66">
-        <v>706802.0</v>
+        <v>706802</v>
       </c>
       <c r="C66">
-        <v>811273.0</v>
+        <v>811273</v>
       </c>
       <c r="D66">
-        <v>997630.0</v>
+        <v>997630</v>
       </c>
       <c r="E66">
-        <v>1163015.0</v>
+        <v>1163015</v>
       </c>
       <c r="F66">
-        <v>1320065.0</v>
+        <v>1320065</v>
       </c>
       <c r="G66">
-        <v>1498622.0</v>
+        <v>1498622</v>
       </c>
       <c r="H66">
-        <v>1605882.0</v>
+        <v>1605882</v>
       </c>
       <c r="I66">
-        <v>1755048.0</v>
+        <v>1755048</v>
       </c>
       <c r="J66">
-        <v>1949713.0</v>
+        <v>1949713</v>
       </c>
       <c r="K66">
-        <v>2177546.0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>2177546</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="s">
         <v>78</v>
       </c>
       <c r="B67">
-        <v>8177.0</v>
+        <v>8177</v>
       </c>
       <c r="C67">
-        <v>17555.0</v>
+        <v>17555</v>
       </c>
       <c r="D67">
-        <v>30089.0</v>
+        <v>30089</v>
       </c>
       <c r="E67">
-        <v>19656.0</v>
+        <v>19656</v>
       </c>
       <c r="F67">
-        <v>19014.0</v>
+        <v>19014</v>
       </c>
       <c r="G67">
-        <v>23640.0</v>
+        <v>23640</v>
       </c>
       <c r="H67">
-        <v>28448.0</v>
+        <v>28448</v>
       </c>
       <c r="I67">
-        <v>31628.0</v>
+        <v>31628</v>
       </c>
       <c r="J67">
-        <v>42121.0</v>
+        <v>42121</v>
       </c>
       <c r="K67">
-        <v>58491.0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+        <v>58491</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>45</v>
       </c>
       <c r="B68">
-        <v>48951.0</v>
+        <v>48951</v>
       </c>
       <c r="C68">
-        <v>60837.0</v>
+        <v>60837</v>
       </c>
       <c r="D68">
-        <v>67561.0</v>
+        <v>67561</v>
       </c>
       <c r="E68">
-        <v>73903.0</v>
+        <v>73903</v>
       </c>
       <c r="F68">
-        <v>81672.0</v>
+        <v>81672</v>
       </c>
       <c r="G68">
-        <v>107778.0</v>
+        <v>107778</v>
       </c>
       <c r="H68">
-        <v>140008.0</v>
+        <v>140008</v>
       </c>
       <c r="I68">
-        <v>152770.0</v>
+        <v>152770</v>
       </c>
       <c r="J68">
-        <v>146062.0</v>
+        <v>146062</v>
       </c>
       <c r="K68">
-        <v>166941.0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+        <v>166941</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B69">
-        <v>3023.0</v>
+        <v>3023</v>
       </c>
       <c r="C69">
-        <v>4255.0</v>
+        <v>4255</v>
       </c>
       <c r="D69">
-        <v>11081.0</v>
+        <v>11081</v>
       </c>
       <c r="E69">
-        <v>30920.0</v>
+        <v>30920</v>
       </c>
       <c r="F69">
-        <v>17397.0</v>
+        <v>17397</v>
       </c>
       <c r="G69">
-        <v>36178.0</v>
+        <v>36178</v>
       </c>
       <c r="H69">
-        <v>68664.0</v>
+        <v>68664</v>
       </c>
       <c r="I69">
-        <v>97225.0</v>
+        <v>97225</v>
       </c>
       <c r="J69">
-        <v>106502.0</v>
+        <v>106502</v>
       </c>
       <c r="K69">
-        <v>145977.0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+        <v>145977</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B70">
-        <v>2958924277.0</v>
+        <v>2958924277</v>
       </c>
       <c r="C70">
-        <v>5921826196.0</v>
+        <v>5921826196</v>
       </c>
       <c r="D70">
-        <v>5925868997.0</v>
+        <v>5925868997</v>
       </c>
       <c r="E70">
-        <v>6338693823.0</v>
+        <v>6338693823</v>
       </c>
       <c r="F70">
-        <v>6762068814.0</v>
+        <v>6762068814</v>
       </c>
       <c r="G70">
-        <v>6765994014.0</v>
+        <v>6765994014</v>
       </c>
       <c r="H70">
-        <v>6766094014.0</v>
+        <v>6766094014</v>
       </c>
       <c r="I70">
-        <v>6766094014.0</v>
+        <v>6766094014</v>
       </c>
       <c r="J70">
-        <v>13532515463.0</v>
+        <v>13532515463</v>
       </c>
       <c r="K70">
-        <v>13532472634.0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+        <v>13532472634</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C71">
-        <v>2959863235.0</v>
+        <v>2959863235</v>
       </c>
       <c r="D71">
-        <v>2959863235.0</v>
+        <v>2959863235</v>
       </c>
       <c r="J71">
-        <v>6766186449.0</v>
+        <v>6766186449</v>
       </c>
       <c r="K71">
-        <v>11955084287.0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+        <v>11955084287</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="E72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="F72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="H72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="I72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="J72">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K72">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="9"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B81" s="16">
-        <v>42825.0</v>
+        <v>42825</v>
       </c>
       <c r="C81" s="16">
-        <v>43190.0</v>
+        <v>43190</v>
       </c>
       <c r="D81" s="16">
-        <v>43555.0</v>
+        <v>43555</v>
       </c>
       <c r="E81" s="16">
-        <v>43921.0</v>
+        <v>43921</v>
       </c>
       <c r="F81" s="16">
-        <v>44286.0</v>
+        <v>44286</v>
       </c>
       <c r="G81" s="16">
-        <v>44651.0</v>
+        <v>44651</v>
       </c>
       <c r="H81" s="16">
-        <v>45016.0</v>
+        <v>45016</v>
       </c>
       <c r="I81" s="16">
-        <v>45382.0</v>
+        <v>45382</v>
       </c>
       <c r="J81" s="16">
-        <v>45747.0</v>
+        <v>45747</v>
       </c>
       <c r="K81" s="16">
-        <v>46112.0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B82">
-        <v>49550.0</v>
+        <v>49550</v>
       </c>
       <c r="C82">
-        <v>71459.0</v>
+        <v>71459</v>
       </c>
       <c r="D82">
-        <v>42346.0</v>
+        <v>42346</v>
       </c>
       <c r="E82">
-        <v>94877.0</v>
+        <v>94877</v>
       </c>
       <c r="F82">
-        <v>26958.0</v>
+        <v>26958</v>
       </c>
       <c r="G82">
-        <v>110654.0</v>
+        <v>110654</v>
       </c>
       <c r="H82">
-        <v>115032.0</v>
+        <v>115032</v>
       </c>
       <c r="I82">
-        <v>158788.0</v>
+        <v>158788</v>
       </c>
       <c r="J82">
-        <v>178703.0</v>
+        <v>178703</v>
       </c>
       <c r="K82">
-        <v>192113.0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>192113</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B83">
-        <v>-66201.0</v>
+        <v>-66201</v>
       </c>
       <c r="C83">
-        <v>-68192.0</v>
+        <v>-68192</v>
       </c>
       <c r="D83">
-        <v>-94507.0</v>
+        <v>-94507</v>
       </c>
       <c r="E83">
-        <v>-72497.0</v>
+        <v>-72497</v>
       </c>
       <c r="F83">
-        <v>-142385.0</v>
+        <v>-142385</v>
       </c>
       <c r="G83">
-        <v>-109162.0</v>
+        <v>-109162</v>
       </c>
       <c r="H83">
-        <v>-93001.0</v>
+        <v>-93001</v>
       </c>
       <c r="I83">
-        <v>-113581.0</v>
+        <v>-113581</v>
       </c>
       <c r="J83">
-        <v>-137535.0</v>
+        <v>-137535</v>
       </c>
       <c r="K83">
-        <v>-101089.0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.2">
+        <v>-101089</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
         <v>34</v>
       </c>
       <c r="B84">
-        <v>8617.0</v>
+        <v>8617</v>
       </c>
       <c r="C84">
-        <v>-2001.0</v>
+        <v>-2001</v>
       </c>
       <c r="D84">
-        <v>55906.0</v>
+        <v>55906</v>
       </c>
       <c r="E84">
-        <v>-2541.0</v>
+        <v>-2541</v>
       </c>
       <c r="F84">
-        <v>101904.0</v>
+        <v>101904</v>
       </c>
       <c r="G84">
-        <v>17289.0</v>
+        <v>17289</v>
       </c>
       <c r="H84">
-        <v>10455.0</v>
+        <v>10455</v>
       </c>
       <c r="I84">
-        <v>-16646.0</v>
+        <v>-16646</v>
       </c>
       <c r="J84">
-        <v>-31891.0</v>
+        <v>-31891</v>
       </c>
       <c r="K84">
-        <v>-51549.0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>-51549</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B85">
-        <v>-8034.0</v>
+        <v>-8034</v>
       </c>
       <c r="C85">
-        <v>1266.0</v>
+        <v>1266</v>
       </c>
       <c r="D85">
-        <v>3745.0</v>
+        <v>3745</v>
       </c>
       <c r="E85">
-        <v>19839.0</v>
+        <v>19839</v>
       </c>
       <c r="F85">
-        <v>-13523.0</v>
+        <v>-13523</v>
       </c>
       <c r="G85">
-        <v>18781.0</v>
+        <v>18781</v>
       </c>
       <c r="H85">
-        <v>32486.0</v>
+        <v>32486</v>
       </c>
       <c r="I85">
-        <v>28561.0</v>
+        <v>28561</v>
       </c>
       <c r="J85">
-        <v>9277.0</v>
+        <v>9277</v>
       </c>
       <c r="K85">
-        <v>39475.0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+        <v>39475</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="9"/>
     </row>
-    <row r="90" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B90">
-        <v>300.09</v>
+        <v>300.08999999999997</v>
       </c>
       <c r="C90">
         <v>401.08</v>
       </c>
       <c r="D90">
-        <v>619.43</v>
+        <v>619.42999999999995</v>
       </c>
       <c r="E90">
         <v>506.06</v>
@@ -5840,18 +6400,18 @@
         <v>1485.85</v>
       </c>
       <c r="J90">
-        <v>1275.1</v>
+        <v>1275.0999999999999</v>
       </c>
       <c r="K90">
         <v>1343.9</v>
       </c>
     </row>
-    <row r="92" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
         <v>89</v>
       </c>
@@ -5868,7 +6428,7 @@
         <v>1352.37</v>
       </c>
       <c r="F93" s="31">
-        <v>1267.89</v>
+        <v>1267.8900000000001</v>
       </c>
       <c r="G93" s="31">
         <v>1352.98</v>
